--- a/2lit_online.xlsx
+++ b/2lit_online.xlsx
@@ -15,12 +15,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="79">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="48">
   <si>
     <t>ناجح ✓</t>
   </si>
   <si>
-    <t>2026-02-26 16:01</t>
+    <t>2026-03-06 16:19</t>
   </si>
   <si>
     <t>80.0%</t>
@@ -29,172 +29,79 @@
     <t>-</t>
   </si>
   <si>
-    <t>01099284562</t>
-  </si>
-  <si>
-    <t>samehsami9@gmail.com</t>
-  </si>
-  <si>
-    <t>Mariam sameh sami</t>
-  </si>
-  <si>
-    <t>2026-02-26 21:29</t>
+    <t>01154109786</t>
+  </si>
+  <si>
+    <t>nadaaseleem@gmail.com</t>
+  </si>
+  <si>
+    <t>Nada Ahmed Seleem</t>
+  </si>
+  <si>
+    <t>2026-03-06 22:25</t>
+  </si>
+  <si>
+    <t>60.0%</t>
+  </si>
+  <si>
+    <t>01032168419</t>
+  </si>
+  <si>
+    <t>shereefelguindi@gmail.com</t>
+  </si>
+  <si>
+    <t>شريف عادل خيرت</t>
+  </si>
+  <si>
+    <t>2026-03-07 23:17</t>
+  </si>
+  <si>
+    <t>01115527889</t>
+  </si>
+  <si>
+    <t>Lomasalma@icloud.com</t>
+  </si>
+  <si>
+    <t>سلمي اشرف عبدالحيم علي</t>
+  </si>
+  <si>
+    <t>2026-03-08 03:35</t>
   </si>
   <si>
     <t>100.0%</t>
   </si>
   <si>
-    <t>01280132743</t>
-  </si>
-  <si>
-    <t>mohamedmos615@gmail.com</t>
-  </si>
-  <si>
-    <t>محمد مصطفى أحمد</t>
-  </si>
-  <si>
-    <t>2026-02-27 15:53</t>
-  </si>
-  <si>
-    <t>01115527889</t>
-  </si>
-  <si>
-    <t>Lomasalma@icloud.com</t>
-  </si>
-  <si>
-    <t>سلمي اشرف عبدالحيم علي</t>
-  </si>
-  <si>
-    <t>2026-02-27 23:29</t>
-  </si>
-  <si>
-    <t>01013657697</t>
-  </si>
-  <si>
-    <t>reemreda1022010@gmail.com</t>
-  </si>
-  <si>
-    <t>reem reda Mohamed</t>
-  </si>
-  <si>
-    <t>01016892333</t>
-  </si>
-  <si>
-    <t>mostafajudy88@gmail.com</t>
-  </si>
-  <si>
-    <t>Judy</t>
-  </si>
-  <si>
-    <t>2026-02-28 11:00</t>
-  </si>
-  <si>
-    <t>01551501457</t>
-  </si>
-  <si>
-    <t>roaaahmed21080001@gmail.com</t>
-  </si>
-  <si>
-    <t>رؤى احمد حسين</t>
-  </si>
-  <si>
-    <t>2026-02-28 12:23</t>
-  </si>
-  <si>
-    <t>01013377375</t>
-  </si>
-  <si>
-    <t>btsfangirlforever6@gmail.com</t>
-  </si>
-  <si>
-    <t>حنين محمد محمود</t>
-  </si>
-  <si>
-    <t>2026-02-28 13:45</t>
-  </si>
-  <si>
-    <t>01090635624</t>
-  </si>
-  <si>
-    <t>yasser1062008@gmail.com</t>
-  </si>
-  <si>
-    <t>Yasser Mohamed fayez</t>
-  </si>
-  <si>
-    <t>2026-02-28 14:22</t>
-  </si>
-  <si>
-    <t>01033050201</t>
-  </si>
-  <si>
-    <t>abdelfatahebrahim38@gmail.com</t>
-  </si>
-  <si>
-    <t>ابراهيم عبدالفتاح فؤاد</t>
-  </si>
-  <si>
-    <t>2026-02-28 17:46</t>
-  </si>
-  <si>
-    <t>60.0%</t>
-  </si>
-  <si>
-    <t>01032168419</t>
-  </si>
-  <si>
-    <t>shereefelguindi@gmail.com</t>
-  </si>
-  <si>
-    <t>شريف عادل خيرت</t>
-  </si>
-  <si>
-    <t>2026-02-28 20:54</t>
-  </si>
-  <si>
-    <t>01101238555</t>
-  </si>
-  <si>
-    <t>mo7ameda7med150@gmail.com</t>
-  </si>
-  <si>
-    <t>محمد احمد نبيل</t>
-  </si>
-  <si>
-    <t>2026-02-28 22:40</t>
-  </si>
-  <si>
-    <t>01091828377</t>
-  </si>
-  <si>
-    <t>yossefshref2009@gmail.com</t>
-  </si>
-  <si>
-    <t>Youssef sherif youssef</t>
-  </si>
-  <si>
-    <t>2026-02-28 23:15</t>
-  </si>
-  <si>
-    <t>01026933947</t>
-  </si>
-  <si>
-    <t>malaksamykamel2008@gmail.com</t>
-  </si>
-  <si>
-    <t>Malak Samy</t>
-  </si>
-  <si>
-    <t>2026-03-01 04:45</t>
-  </si>
-  <si>
-    <t>01225131890</t>
-  </si>
-  <si>
-    <t>ganalh66@gmail.com</t>
-  </si>
-  <si>
-    <t>Jana Khalil ebrahim</t>
+    <t>01128207402</t>
+  </si>
+  <si>
+    <t>hoba.maamon@gmail.com</t>
+  </si>
+  <si>
+    <t>سما أسامه محمد منصور</t>
+  </si>
+  <si>
+    <t>2026-03-08 15:32</t>
+  </si>
+  <si>
+    <t>01013764074</t>
+  </si>
+  <si>
+    <t>nadayusuf2010@gmail.com</t>
+  </si>
+  <si>
+    <t>ندى يوسف عبدالله</t>
+  </si>
+  <si>
+    <t>2026-03-08 16:37</t>
+  </si>
+  <si>
+    <t>01272078171</t>
+  </si>
+  <si>
+    <t>ma7163874@gmail.com</t>
+  </si>
+  <si>
+    <t>مريم احمد على محمد</t>
   </si>
   <si>
     <t>الحالة</t>
@@ -245,13 +152,13 @@
     <t>#</t>
   </si>
   <si>
-    <t>نتائج الامتحان: Quiz 3 Pure - 2nd Term - Online</t>
+    <t>نتائج الامتحان: Quiz 4 Pure - 2nd Term - Online</t>
   </si>
   <si>
     <t>الدرجة الكاملة: 10 | درجة النجاح: 5.00</t>
   </si>
   <si>
-    <t>تاريخ التصدير: 2026-03-01 14:01</t>
+    <t>تاريخ التصدير: 2026-03-08 19:44</t>
   </si>
 </sst>
 </file>
@@ -639,7 +546,7 @@
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
   </sheetPr>
-  <dimension ref="A1:P18"/>
+  <dimension ref="A1:P10"/>
   <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col min="1" max="1" width="6" customWidth="true" style="0"/>
@@ -662,67 +569,67 @@
   <sheetData>
     <row r="1" spans="1:16">
       <c r="A1" s="3" t="s">
-        <v>76</v>
+        <v>45</v>
       </c>
     </row>
     <row r="2" spans="1:16">
       <c r="A2" s="3" t="s">
-        <v>77</v>
+        <v>46</v>
       </c>
     </row>
     <row r="3" spans="1:16">
       <c r="A3" s="3" t="s">
-        <v>78</v>
+        <v>47</v>
       </c>
     </row>
     <row r="4" spans="1:16">
       <c r="A4" s="1" t="s">
-        <v>75</v>
+        <v>44</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>74</v>
+        <v>43</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>73</v>
+        <v>42</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>72</v>
+        <v>41</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>71</v>
+        <v>40</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>70</v>
+        <v>39</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>69</v>
+        <v>38</v>
       </c>
       <c r="H4" s="1" t="s">
-        <v>68</v>
+        <v>37</v>
       </c>
       <c r="I4" s="1" t="s">
-        <v>67</v>
+        <v>36</v>
       </c>
       <c r="J4" s="1" t="s">
-        <v>66</v>
+        <v>35</v>
       </c>
       <c r="K4" s="1" t="s">
-        <v>65</v>
+        <v>34</v>
       </c>
       <c r="L4" s="1" t="s">
-        <v>64</v>
+        <v>33</v>
       </c>
       <c r="M4" s="1" t="s">
-        <v>63</v>
+        <v>32</v>
       </c>
       <c r="N4" s="1" t="s">
-        <v>62</v>
+        <v>31</v>
       </c>
       <c r="O4" s="1" t="s">
-        <v>61</v>
+        <v>30</v>
       </c>
       <c r="P4" s="1" t="s">
-        <v>60</v>
+        <v>29</v>
       </c>
     </row>
     <row r="5" spans="1:16">
@@ -730,13 +637,13 @@
         <v>1</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>59</v>
+        <v>28</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>58</v>
+        <v>27</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>57</v>
+        <v>26</v>
       </c>
       <c r="E5" s="2" t="s">
         <v>3</v>
@@ -745,29 +652,29 @@
         <v>1</v>
       </c>
       <c r="G5" s="2">
-        <v>6.0</v>
+        <v>8.0</v>
       </c>
       <c r="H5" s="2">
         <v>10.0</v>
       </c>
       <c r="I5" s="2" t="s">
-        <v>40</v>
+        <v>2</v>
       </c>
       <c r="J5" s="2">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K5" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L5" s="2"/>
       <c r="M5" s="2">
         <v>5</v>
       </c>
       <c r="N5" s="2">
-        <v>6.28</v>
+        <v>3.87</v>
       </c>
       <c r="O5" s="2" t="s">
-        <v>56</v>
+        <v>25</v>
       </c>
       <c r="P5" s="2" t="s">
         <v>0</v>
@@ -778,42 +685,44 @@
         <v>2</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>55</v>
+        <v>24</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>54</v>
+        <v>23</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>53</v>
+        <v>22</v>
       </c>
       <c r="E6" s="2" t="s">
         <v>3</v>
       </c>
       <c r="F6" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G6" s="2">
-        <v>10.0</v>
+        <v>8.0</v>
       </c>
       <c r="H6" s="2">
         <v>10.0</v>
       </c>
       <c r="I6" s="2" t="s">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="J6" s="2">
-        <v>5</v>
-      </c>
-      <c r="K6" s="2"/>
+        <v>4</v>
+      </c>
+      <c r="K6" s="2">
+        <v>1</v>
+      </c>
       <c r="L6" s="2"/>
       <c r="M6" s="2">
         <v>5</v>
       </c>
       <c r="N6" s="2">
-        <v>5.1</v>
+        <v>16.37</v>
       </c>
       <c r="O6" s="2" t="s">
-        <v>52</v>
+        <v>21</v>
       </c>
       <c r="P6" s="2" t="s">
         <v>0</v>
@@ -824,13 +733,13 @@
         <v>3</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>51</v>
+        <v>20</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>50</v>
+        <v>19</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>49</v>
+        <v>18</v>
       </c>
       <c r="E7" s="2" t="s">
         <v>3</v>
@@ -839,29 +748,27 @@
         <v>1</v>
       </c>
       <c r="G7" s="2">
-        <v>8.0</v>
+        <v>10.0</v>
       </c>
       <c r="H7" s="2">
         <v>10.0</v>
       </c>
       <c r="I7" s="2" t="s">
-        <v>2</v>
+        <v>17</v>
       </c>
       <c r="J7" s="2">
-        <v>4</v>
-      </c>
-      <c r="K7" s="2">
-        <v>1</v>
-      </c>
+        <v>5</v>
+      </c>
+      <c r="K7" s="2"/>
       <c r="L7" s="2"/>
       <c r="M7" s="2">
         <v>5</v>
       </c>
       <c r="N7" s="2">
-        <v>3.77</v>
+        <v>9.97</v>
       </c>
       <c r="O7" s="2" t="s">
-        <v>48</v>
+        <v>16</v>
       </c>
       <c r="P7" s="2" t="s">
         <v>0</v>
@@ -872,13 +779,13 @@
         <v>4</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>47</v>
+        <v>15</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>46</v>
+        <v>14</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>45</v>
+        <v>13</v>
       </c>
       <c r="E8" s="2" t="s">
         <v>3</v>
@@ -893,7 +800,7 @@
         <v>10.0</v>
       </c>
       <c r="I8" s="2" t="s">
-        <v>40</v>
+        <v>8</v>
       </c>
       <c r="J8" s="2">
         <v>3</v>
@@ -906,10 +813,10 @@
         <v>5</v>
       </c>
       <c r="N8" s="2">
-        <v>6.03</v>
+        <v>7.03</v>
       </c>
       <c r="O8" s="2" t="s">
-        <v>44</v>
+        <v>12</v>
       </c>
       <c r="P8" s="2" t="s">
         <v>0</v>
@@ -920,13 +827,13 @@
         <v>5</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>43</v>
+        <v>11</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>42</v>
+        <v>10</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>41</v>
+        <v>9</v>
       </c>
       <c r="E9" s="2" t="s">
         <v>3</v>
@@ -941,7 +848,7 @@
         <v>10.0</v>
       </c>
       <c r="I9" s="2" t="s">
-        <v>40</v>
+        <v>8</v>
       </c>
       <c r="J9" s="2">
         <v>3</v>
@@ -954,10 +861,10 @@
         <v>5</v>
       </c>
       <c r="N9" s="2">
-        <v>30.0</v>
+        <v>31.33</v>
       </c>
       <c r="O9" s="2" t="s">
-        <v>39</v>
+        <v>7</v>
       </c>
       <c r="P9" s="2" t="s">
         <v>0</v>
@@ -968,13 +875,13 @@
         <v>6</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>38</v>
+        <v>6</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>37</v>
+        <v>5</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>36</v>
+        <v>4</v>
       </c>
       <c r="E10" s="2" t="s">
         <v>3</v>
@@ -1002,386 +909,12 @@
         <v>5</v>
       </c>
       <c r="N10" s="2">
-        <v>9.4</v>
+        <v>4.08</v>
       </c>
       <c r="O10" s="2" t="s">
-        <v>35</v>
+        <v>1</v>
       </c>
       <c r="P10" s="2" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11" spans="1:16">
-      <c r="A11" s="2">
-        <v>7</v>
-      </c>
-      <c r="B11" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="C11" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="D11" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="E11" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="F11" s="2">
-        <v>1</v>
-      </c>
-      <c r="G11" s="2">
-        <v>10.0</v>
-      </c>
-      <c r="H11" s="2">
-        <v>10.0</v>
-      </c>
-      <c r="I11" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="J11" s="2">
-        <v>5</v>
-      </c>
-      <c r="K11" s="2"/>
-      <c r="L11" s="2"/>
-      <c r="M11" s="2">
-        <v>5</v>
-      </c>
-      <c r="N11" s="2">
-        <v>9.08</v>
-      </c>
-      <c r="O11" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="P11" s="2" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="12" spans="1:16">
-      <c r="A12" s="2">
-        <v>8</v>
-      </c>
-      <c r="B12" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="C12" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="D12" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="E12" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="F12" s="2">
-        <v>1</v>
-      </c>
-      <c r="G12" s="2">
-        <v>10.0</v>
-      </c>
-      <c r="H12" s="2">
-        <v>10.0</v>
-      </c>
-      <c r="I12" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="J12" s="2">
-        <v>5</v>
-      </c>
-      <c r="K12" s="2"/>
-      <c r="L12" s="2"/>
-      <c r="M12" s="2">
-        <v>5</v>
-      </c>
-      <c r="N12" s="2">
-        <v>9.42</v>
-      </c>
-      <c r="O12" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="P12" s="2" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="13" spans="1:16">
-      <c r="A13" s="2">
-        <v>9</v>
-      </c>
-      <c r="B13" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="C13" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="D13" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="E13" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="F13" s="2">
-        <v>2</v>
-      </c>
-      <c r="G13" s="2">
-        <v>8.0</v>
-      </c>
-      <c r="H13" s="2">
-        <v>10.0</v>
-      </c>
-      <c r="I13" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="J13" s="2">
-        <v>4</v>
-      </c>
-      <c r="K13" s="2">
-        <v>1</v>
-      </c>
-      <c r="L13" s="2"/>
-      <c r="M13" s="2">
-        <v>5</v>
-      </c>
-      <c r="N13" s="2">
-        <v>4.92</v>
-      </c>
-      <c r="O13" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="P13" s="2" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="14" spans="1:16">
-      <c r="A14" s="2">
-        <v>10</v>
-      </c>
-      <c r="B14" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="C14" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="D14" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="E14" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="F14" s="2">
-        <v>1</v>
-      </c>
-      <c r="G14" s="2">
-        <v>8.0</v>
-      </c>
-      <c r="H14" s="2">
-        <v>10.0</v>
-      </c>
-      <c r="I14" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="J14" s="2">
-        <v>4</v>
-      </c>
-      <c r="K14" s="2">
-        <v>1</v>
-      </c>
-      <c r="L14" s="2"/>
-      <c r="M14" s="2">
-        <v>5</v>
-      </c>
-      <c r="N14" s="2">
-        <v>1.83</v>
-      </c>
-      <c r="O14" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="P14" s="2" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15" spans="1:16">
-      <c r="A15" s="2">
-        <v>11</v>
-      </c>
-      <c r="B15" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="C15" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="D15" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="E15" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="F15" s="2">
-        <v>1</v>
-      </c>
-      <c r="G15" s="2">
-        <v>10.0</v>
-      </c>
-      <c r="H15" s="2">
-        <v>10.0</v>
-      </c>
-      <c r="I15" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="J15" s="2">
-        <v>5</v>
-      </c>
-      <c r="K15" s="2"/>
-      <c r="L15" s="2"/>
-      <c r="M15" s="2">
-        <v>5</v>
-      </c>
-      <c r="N15" s="2">
-        <v>6.72</v>
-      </c>
-      <c r="O15" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="P15" s="2" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="16" spans="1:16">
-      <c r="A16" s="2">
-        <v>12</v>
-      </c>
-      <c r="B16" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="C16" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="D16" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="E16" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="F16" s="2">
-        <v>1</v>
-      </c>
-      <c r="G16" s="2">
-        <v>10.0</v>
-      </c>
-      <c r="H16" s="2">
-        <v>10.0</v>
-      </c>
-      <c r="I16" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="J16" s="2">
-        <v>5</v>
-      </c>
-      <c r="K16" s="2"/>
-      <c r="L16" s="2"/>
-      <c r="M16" s="2">
-        <v>5</v>
-      </c>
-      <c r="N16" s="2">
-        <v>8.73</v>
-      </c>
-      <c r="O16" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="P16" s="2" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="17" spans="1:16">
-      <c r="A17" s="2">
-        <v>13</v>
-      </c>
-      <c r="B17" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="C17" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="D17" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="E17" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="F17" s="2">
-        <v>1</v>
-      </c>
-      <c r="G17" s="2">
-        <v>10.0</v>
-      </c>
-      <c r="H17" s="2">
-        <v>10.0</v>
-      </c>
-      <c r="I17" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="J17" s="2">
-        <v>5</v>
-      </c>
-      <c r="K17" s="2"/>
-      <c r="L17" s="2"/>
-      <c r="M17" s="2">
-        <v>5</v>
-      </c>
-      <c r="N17" s="2">
-        <v>14.1</v>
-      </c>
-      <c r="O17" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="P17" s="2" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="18" spans="1:16">
-      <c r="A18" s="2">
-        <v>14</v>
-      </c>
-      <c r="B18" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="C18" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="D18" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="E18" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="F18" s="2">
-        <v>2</v>
-      </c>
-      <c r="G18" s="2">
-        <v>8.0</v>
-      </c>
-      <c r="H18" s="2">
-        <v>10.0</v>
-      </c>
-      <c r="I18" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="J18" s="2">
-        <v>4</v>
-      </c>
-      <c r="K18" s="2">
-        <v>1</v>
-      </c>
-      <c r="L18" s="2"/>
-      <c r="M18" s="2">
-        <v>5</v>
-      </c>
-      <c r="N18" s="2">
-        <v>10.85</v>
-      </c>
-      <c r="O18" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="P18" s="2" t="s">
         <v>0</v>
       </c>
     </row>

--- a/2lit_online.xlsx
+++ b/2lit_online.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="48">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="68">
   <si>
     <t>ناجح ✓</t>
   </si>
@@ -104,6 +104,66 @@
     <t>مريم احمد على محمد</t>
   </si>
   <si>
+    <t>2026-03-08 21:06</t>
+  </si>
+  <si>
+    <t>01280132743</t>
+  </si>
+  <si>
+    <t>mohamedmos615@gmail.com</t>
+  </si>
+  <si>
+    <t>محمد مصطفى أحمد</t>
+  </si>
+  <si>
+    <t>2026-03-08 20:59</t>
+  </si>
+  <si>
+    <t>01121973130</t>
+  </si>
+  <si>
+    <t>seifzarad50@gmail.com</t>
+  </si>
+  <si>
+    <t>سيف ابراهيم ابوالعنين</t>
+  </si>
+  <si>
+    <t>2026-03-08 22:48</t>
+  </si>
+  <si>
+    <t>01012462274</t>
+  </si>
+  <si>
+    <t>Loujain1356@gmail.com</t>
+  </si>
+  <si>
+    <t>Loujain Osama elsayed</t>
+  </si>
+  <si>
+    <t>2026-03-09 00:43</t>
+  </si>
+  <si>
+    <t>01120749269</t>
+  </si>
+  <si>
+    <t>rokayaelsawy8@gmail.com</t>
+  </si>
+  <si>
+    <t>Rokaya Elsawy</t>
+  </si>
+  <si>
+    <t>2026-03-09 14:36</t>
+  </si>
+  <si>
+    <t>01125509128</t>
+  </si>
+  <si>
+    <t>marwanayman72009@gmail.com</t>
+  </si>
+  <si>
+    <t>مروان ايمن عاطف</t>
+  </si>
+  <si>
     <t>الحالة</t>
   </si>
   <si>
@@ -158,7 +218,7 @@
     <t>الدرجة الكاملة: 10 | درجة النجاح: 5.00</t>
   </si>
   <si>
-    <t>تاريخ التصدير: 2026-03-08 19:44</t>
+    <t>تاريخ التصدير: 2026-03-09 19:29</t>
   </si>
 </sst>
 </file>
@@ -546,7 +606,7 @@
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
   </sheetPr>
-  <dimension ref="A1:P10"/>
+  <dimension ref="A1:P15"/>
   <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col min="1" max="1" width="6" customWidth="true" style="0"/>
@@ -569,67 +629,67 @@
   <sheetData>
     <row r="1" spans="1:16">
       <c r="A1" s="3" t="s">
-        <v>45</v>
+        <v>65</v>
       </c>
     </row>
     <row r="2" spans="1:16">
       <c r="A2" s="3" t="s">
-        <v>46</v>
+        <v>66</v>
       </c>
     </row>
     <row r="3" spans="1:16">
       <c r="A3" s="3" t="s">
-        <v>47</v>
+        <v>67</v>
       </c>
     </row>
     <row r="4" spans="1:16">
       <c r="A4" s="1" t="s">
-        <v>44</v>
+        <v>64</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>43</v>
+        <v>63</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>42</v>
+        <v>62</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>41</v>
+        <v>61</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>40</v>
+        <v>60</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>39</v>
+        <v>59</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>38</v>
+        <v>58</v>
       </c>
       <c r="H4" s="1" t="s">
-        <v>37</v>
+        <v>57</v>
       </c>
       <c r="I4" s="1" t="s">
-        <v>36</v>
+        <v>56</v>
       </c>
       <c r="J4" s="1" t="s">
-        <v>35</v>
+        <v>55</v>
       </c>
       <c r="K4" s="1" t="s">
-        <v>34</v>
+        <v>54</v>
       </c>
       <c r="L4" s="1" t="s">
-        <v>33</v>
+        <v>53</v>
       </c>
       <c r="M4" s="1" t="s">
-        <v>32</v>
+        <v>52</v>
       </c>
       <c r="N4" s="1" t="s">
-        <v>31</v>
+        <v>51</v>
       </c>
       <c r="O4" s="1" t="s">
-        <v>30</v>
+        <v>50</v>
       </c>
       <c r="P4" s="1" t="s">
-        <v>29</v>
+        <v>49</v>
       </c>
     </row>
     <row r="5" spans="1:16">
@@ -637,44 +697,44 @@
         <v>1</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>28</v>
+        <v>48</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>27</v>
+        <v>47</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>26</v>
+        <v>46</v>
       </c>
       <c r="E5" s="2" t="s">
         <v>3</v>
       </c>
       <c r="F5" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G5" s="2">
-        <v>8.0</v>
+        <v>6.0</v>
       </c>
       <c r="H5" s="2">
         <v>10.0</v>
       </c>
       <c r="I5" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="J5" s="2">
+        <v>3</v>
+      </c>
+      <c r="K5" s="2">
         <v>2</v>
-      </c>
-      <c r="J5" s="2">
-        <v>4</v>
-      </c>
-      <c r="K5" s="2">
-        <v>1</v>
       </c>
       <c r="L5" s="2"/>
       <c r="M5" s="2">
         <v>5</v>
       </c>
       <c r="N5" s="2">
-        <v>3.87</v>
+        <v>4.75</v>
       </c>
       <c r="O5" s="2" t="s">
-        <v>25</v>
+        <v>45</v>
       </c>
       <c r="P5" s="2" t="s">
         <v>0</v>
@@ -685,44 +745,42 @@
         <v>2</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>24</v>
+        <v>44</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>23</v>
+        <v>43</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>22</v>
+        <v>42</v>
       </c>
       <c r="E6" s="2" t="s">
         <v>3</v>
       </c>
       <c r="F6" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G6" s="2">
-        <v>8.0</v>
+        <v>10.0</v>
       </c>
       <c r="H6" s="2">
         <v>10.0</v>
       </c>
       <c r="I6" s="2" t="s">
-        <v>2</v>
+        <v>17</v>
       </c>
       <c r="J6" s="2">
-        <v>4</v>
-      </c>
-      <c r="K6" s="2">
-        <v>1</v>
-      </c>
+        <v>5</v>
+      </c>
+      <c r="K6" s="2"/>
       <c r="L6" s="2"/>
       <c r="M6" s="2">
         <v>5</v>
       </c>
       <c r="N6" s="2">
-        <v>16.37</v>
+        <v>4.35</v>
       </c>
       <c r="O6" s="2" t="s">
-        <v>21</v>
+        <v>41</v>
       </c>
       <c r="P6" s="2" t="s">
         <v>0</v>
@@ -733,13 +791,13 @@
         <v>3</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>20</v>
+        <v>40</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>19</v>
+        <v>39</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>18</v>
+        <v>38</v>
       </c>
       <c r="E7" s="2" t="s">
         <v>3</v>
@@ -765,10 +823,10 @@
         <v>5</v>
       </c>
       <c r="N7" s="2">
-        <v>9.97</v>
+        <v>4.57</v>
       </c>
       <c r="O7" s="2" t="s">
-        <v>16</v>
+        <v>37</v>
       </c>
       <c r="P7" s="2" t="s">
         <v>0</v>
@@ -779,13 +837,13 @@
         <v>4</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>15</v>
+        <v>36</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>14</v>
+        <v>35</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>13</v>
+        <v>34</v>
       </c>
       <c r="E8" s="2" t="s">
         <v>3</v>
@@ -794,29 +852,27 @@
         <v>1</v>
       </c>
       <c r="G8" s="2">
-        <v>6.0</v>
+        <v>10.0</v>
       </c>
       <c r="H8" s="2">
         <v>10.0</v>
       </c>
       <c r="I8" s="2" t="s">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="J8" s="2">
-        <v>3</v>
-      </c>
-      <c r="K8" s="2">
-        <v>2</v>
-      </c>
+        <v>5</v>
+      </c>
+      <c r="K8" s="2"/>
       <c r="L8" s="2"/>
       <c r="M8" s="2">
         <v>5</v>
       </c>
       <c r="N8" s="2">
-        <v>7.03</v>
+        <v>2.07</v>
       </c>
       <c r="O8" s="2" t="s">
-        <v>12</v>
+        <v>33</v>
       </c>
       <c r="P8" s="2" t="s">
         <v>0</v>
@@ -827,44 +883,44 @@
         <v>5</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>11</v>
+        <v>32</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>10</v>
+        <v>31</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>9</v>
+        <v>30</v>
       </c>
       <c r="E9" s="2" t="s">
         <v>3</v>
       </c>
       <c r="F9" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G9" s="2">
-        <v>6.0</v>
+        <v>8.0</v>
       </c>
       <c r="H9" s="2">
         <v>10.0</v>
       </c>
       <c r="I9" s="2" t="s">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="J9" s="2">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K9" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L9" s="2"/>
       <c r="M9" s="2">
         <v>5</v>
       </c>
       <c r="N9" s="2">
-        <v>31.33</v>
+        <v>12.95</v>
       </c>
       <c r="O9" s="2" t="s">
-        <v>7</v>
+        <v>29</v>
       </c>
       <c r="P9" s="2" t="s">
         <v>0</v>
@@ -875,13 +931,13 @@
         <v>6</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>6</v>
+        <v>28</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>5</v>
+        <v>27</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>4</v>
+        <v>26</v>
       </c>
       <c r="E10" s="2" t="s">
         <v>3</v>
@@ -909,12 +965,250 @@
         <v>5</v>
       </c>
       <c r="N10" s="2">
+        <v>3.87</v>
+      </c>
+      <c r="O10" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="P10" s="2" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:16">
+      <c r="A11" s="2">
+        <v>7</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="D11" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="E11" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="F11" s="2">
+        <v>2</v>
+      </c>
+      <c r="G11" s="2">
+        <v>8.0</v>
+      </c>
+      <c r="H11" s="2">
+        <v>10.0</v>
+      </c>
+      <c r="I11" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="J11" s="2">
+        <v>4</v>
+      </c>
+      <c r="K11" s="2">
+        <v>1</v>
+      </c>
+      <c r="L11" s="2"/>
+      <c r="M11" s="2">
+        <v>5</v>
+      </c>
+      <c r="N11" s="2">
+        <v>16.37</v>
+      </c>
+      <c r="O11" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="P11" s="2" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:16">
+      <c r="A12" s="2">
+        <v>8</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="C12" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="D12" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E12" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="F12" s="2">
+        <v>1</v>
+      </c>
+      <c r="G12" s="2">
+        <v>10.0</v>
+      </c>
+      <c r="H12" s="2">
+        <v>10.0</v>
+      </c>
+      <c r="I12" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="J12" s="2">
+        <v>5</v>
+      </c>
+      <c r="K12" s="2"/>
+      <c r="L12" s="2"/>
+      <c r="M12" s="2">
+        <v>5</v>
+      </c>
+      <c r="N12" s="2">
+        <v>9.97</v>
+      </c>
+      <c r="O12" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="P12" s="2" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:16">
+      <c r="A13" s="2">
+        <v>9</v>
+      </c>
+      <c r="B13" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C13" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="D13" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="E13" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="F13" s="2">
+        <v>1</v>
+      </c>
+      <c r="G13" s="2">
+        <v>6.0</v>
+      </c>
+      <c r="H13" s="2">
+        <v>10.0</v>
+      </c>
+      <c r="I13" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="J13" s="2">
+        <v>3</v>
+      </c>
+      <c r="K13" s="2">
+        <v>2</v>
+      </c>
+      <c r="L13" s="2"/>
+      <c r="M13" s="2">
+        <v>5</v>
+      </c>
+      <c r="N13" s="2">
+        <v>7.03</v>
+      </c>
+      <c r="O13" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="P13" s="2" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:16">
+      <c r="A14" s="2">
+        <v>10</v>
+      </c>
+      <c r="B14" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="C14" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D14" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E14" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="F14" s="2">
+        <v>1</v>
+      </c>
+      <c r="G14" s="2">
+        <v>6.0</v>
+      </c>
+      <c r="H14" s="2">
+        <v>10.0</v>
+      </c>
+      <c r="I14" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="J14" s="2">
+        <v>3</v>
+      </c>
+      <c r="K14" s="2">
+        <v>2</v>
+      </c>
+      <c r="L14" s="2"/>
+      <c r="M14" s="2">
+        <v>5</v>
+      </c>
+      <c r="N14" s="2">
+        <v>31.33</v>
+      </c>
+      <c r="O14" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="P14" s="2" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:16">
+      <c r="A15" s="2">
+        <v>11</v>
+      </c>
+      <c r="B15" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="C15" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="D15" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="E15" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="F15" s="2">
+        <v>1</v>
+      </c>
+      <c r="G15" s="2">
+        <v>8.0</v>
+      </c>
+      <c r="H15" s="2">
+        <v>10.0</v>
+      </c>
+      <c r="I15" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="J15" s="2">
+        <v>4</v>
+      </c>
+      <c r="K15" s="2">
+        <v>1</v>
+      </c>
+      <c r="L15" s="2"/>
+      <c r="M15" s="2">
+        <v>5</v>
+      </c>
+      <c r="N15" s="2">
         <v>4.08</v>
       </c>
-      <c r="O10" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="P10" s="2" t="s">
+      <c r="O15" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="P15" s="2" t="s">
         <v>0</v>
       </c>
     </row>

--- a/2lit_online.xlsx
+++ b/2lit_online.xlsx
@@ -15,153 +15,105 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="68">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="52">
   <si>
     <t>ناجح ✓</t>
   </si>
   <si>
-    <t>2026-03-06 16:19</t>
+    <t>2026-03-12 15:09</t>
+  </si>
+  <si>
+    <t>100.0%</t>
+  </si>
+  <si>
+    <t>-</t>
+  </si>
+  <si>
+    <t>01020745750</t>
+  </si>
+  <si>
+    <t>farragyassin4@gmail.com</t>
+  </si>
+  <si>
+    <t>Yassin Farrag</t>
+  </si>
+  <si>
+    <t>2026-03-13 22:16</t>
+  </si>
+  <si>
+    <t>01013377375</t>
+  </si>
+  <si>
+    <t>btsfangirlforever6@gmail.com</t>
+  </si>
+  <si>
+    <t>حنين محمد محمود</t>
+  </si>
+  <si>
+    <t>2026-03-14 13:32</t>
   </si>
   <si>
     <t>80.0%</t>
   </si>
   <si>
-    <t>-</t>
-  </si>
-  <si>
-    <t>01154109786</t>
-  </si>
-  <si>
-    <t>nadaaseleem@gmail.com</t>
-  </si>
-  <si>
-    <t>Nada Ahmed Seleem</t>
-  </si>
-  <si>
-    <t>2026-03-06 22:25</t>
+    <t>01032168419</t>
+  </si>
+  <si>
+    <t>shereefelguindi@gmail.com</t>
+  </si>
+  <si>
+    <t>شريف عادل خيرت</t>
+  </si>
+  <si>
+    <t>2026-03-14 14:05</t>
+  </si>
+  <si>
+    <t>01280132743</t>
+  </si>
+  <si>
+    <t>mohamedmos615@gmail.com</t>
+  </si>
+  <si>
+    <t>محمد مصطفى أحمد</t>
+  </si>
+  <si>
+    <t>2026-03-14 17:29</t>
+  </si>
+  <si>
+    <t>01272078171</t>
+  </si>
+  <si>
+    <t>ma7163874@gmail.com</t>
+  </si>
+  <si>
+    <t>مريم احمد على محمد</t>
+  </si>
+  <si>
+    <t>2026-03-14 22:10</t>
+  </si>
+  <si>
+    <t>01101238555</t>
+  </si>
+  <si>
+    <t>mo7ameda7med150@gmail.com</t>
+  </si>
+  <si>
+    <t>محمد احمد نبيل</t>
+  </si>
+  <si>
+    <t>2026-03-15 15:52</t>
   </si>
   <si>
     <t>60.0%</t>
   </si>
   <si>
-    <t>01032168419</t>
-  </si>
-  <si>
-    <t>shereefelguindi@gmail.com</t>
-  </si>
-  <si>
-    <t>شريف عادل خيرت</t>
-  </si>
-  <si>
-    <t>2026-03-07 23:17</t>
-  </si>
-  <si>
-    <t>01115527889</t>
-  </si>
-  <si>
-    <t>Lomasalma@icloud.com</t>
-  </si>
-  <si>
-    <t>سلمي اشرف عبدالحيم علي</t>
-  </si>
-  <si>
-    <t>2026-03-08 03:35</t>
-  </si>
-  <si>
-    <t>100.0%</t>
-  </si>
-  <si>
-    <t>01128207402</t>
-  </si>
-  <si>
-    <t>hoba.maamon@gmail.com</t>
-  </si>
-  <si>
-    <t>سما أسامه محمد منصور</t>
-  </si>
-  <si>
-    <t>2026-03-08 15:32</t>
-  </si>
-  <si>
-    <t>01013764074</t>
-  </si>
-  <si>
-    <t>nadayusuf2010@gmail.com</t>
-  </si>
-  <si>
-    <t>ندى يوسف عبدالله</t>
-  </si>
-  <si>
-    <t>2026-03-08 16:37</t>
-  </si>
-  <si>
-    <t>01272078171</t>
-  </si>
-  <si>
-    <t>ma7163874@gmail.com</t>
-  </si>
-  <si>
-    <t>مريم احمد على محمد</t>
-  </si>
-  <si>
-    <t>2026-03-08 21:06</t>
-  </si>
-  <si>
-    <t>01280132743</t>
-  </si>
-  <si>
-    <t>mohamedmos615@gmail.com</t>
-  </si>
-  <si>
-    <t>محمد مصطفى أحمد</t>
-  </si>
-  <si>
-    <t>2026-03-08 20:59</t>
-  </si>
-  <si>
-    <t>01121973130</t>
-  </si>
-  <si>
-    <t>seifzarad50@gmail.com</t>
-  </si>
-  <si>
-    <t>سيف ابراهيم ابوالعنين</t>
-  </si>
-  <si>
-    <t>2026-03-08 22:48</t>
-  </si>
-  <si>
-    <t>01012462274</t>
-  </si>
-  <si>
-    <t>Loujain1356@gmail.com</t>
-  </si>
-  <si>
-    <t>Loujain Osama elsayed</t>
-  </si>
-  <si>
-    <t>2026-03-09 00:43</t>
-  </si>
-  <si>
-    <t>01120749269</t>
-  </si>
-  <si>
-    <t>rokayaelsawy8@gmail.com</t>
-  </si>
-  <si>
-    <t>Rokaya Elsawy</t>
-  </si>
-  <si>
-    <t>2026-03-09 14:36</t>
-  </si>
-  <si>
-    <t>01125509128</t>
-  </si>
-  <si>
-    <t>marwanayman72009@gmail.com</t>
-  </si>
-  <si>
-    <t>مروان ايمن عاطف</t>
+    <t>01210081096</t>
+  </si>
+  <si>
+    <t>malaak.7assan100@gmail.com</t>
+  </si>
+  <si>
+    <t>Malak Hassan</t>
   </si>
   <si>
     <t>الحالة</t>
@@ -212,13 +164,13 @@
     <t>#</t>
   </si>
   <si>
-    <t>نتائج الامتحان: Quiz 4 Pure - 2nd Term - Online</t>
+    <t>نتائج الامتحان: Quiz 5 Pure - 2nd Term - Online</t>
   </si>
   <si>
     <t>الدرجة الكاملة: 10 | درجة النجاح: 5.00</t>
   </si>
   <si>
-    <t>تاريخ التصدير: 2026-03-09 19:29</t>
+    <t>تاريخ التصدير: 2026-03-15 19:18</t>
   </si>
 </sst>
 </file>
@@ -606,7 +558,7 @@
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
   </sheetPr>
-  <dimension ref="A1:P15"/>
+  <dimension ref="A1:P11"/>
   <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col min="1" max="1" width="6" customWidth="true" style="0"/>
@@ -629,67 +581,67 @@
   <sheetData>
     <row r="1" spans="1:16">
       <c r="A1" s="3" t="s">
-        <v>65</v>
+        <v>49</v>
       </c>
     </row>
     <row r="2" spans="1:16">
       <c r="A2" s="3" t="s">
-        <v>66</v>
+        <v>50</v>
       </c>
     </row>
     <row r="3" spans="1:16">
       <c r="A3" s="3" t="s">
-        <v>67</v>
+        <v>51</v>
       </c>
     </row>
     <row r="4" spans="1:16">
       <c r="A4" s="1" t="s">
-        <v>64</v>
+        <v>48</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>63</v>
+        <v>47</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>62</v>
+        <v>46</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>61</v>
+        <v>45</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>60</v>
+        <v>44</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>59</v>
+        <v>43</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>58</v>
+        <v>42</v>
       </c>
       <c r="H4" s="1" t="s">
-        <v>57</v>
+        <v>41</v>
       </c>
       <c r="I4" s="1" t="s">
-        <v>56</v>
+        <v>40</v>
       </c>
       <c r="J4" s="1" t="s">
-        <v>55</v>
+        <v>39</v>
       </c>
       <c r="K4" s="1" t="s">
-        <v>54</v>
+        <v>38</v>
       </c>
       <c r="L4" s="1" t="s">
-        <v>53</v>
+        <v>37</v>
       </c>
       <c r="M4" s="1" t="s">
-        <v>52</v>
+        <v>36</v>
       </c>
       <c r="N4" s="1" t="s">
-        <v>51</v>
+        <v>35</v>
       </c>
       <c r="O4" s="1" t="s">
-        <v>50</v>
+        <v>34</v>
       </c>
       <c r="P4" s="1" t="s">
-        <v>49</v>
+        <v>33</v>
       </c>
     </row>
     <row r="5" spans="1:16">
@@ -697,19 +649,19 @@
         <v>1</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>48</v>
+        <v>32</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>47</v>
+        <v>31</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>46</v>
+        <v>30</v>
       </c>
       <c r="E5" s="2" t="s">
         <v>3</v>
       </c>
       <c r="F5" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G5" s="2">
         <v>6.0</v>
@@ -718,7 +670,7 @@
         <v>10.0</v>
       </c>
       <c r="I5" s="2" t="s">
-        <v>8</v>
+        <v>29</v>
       </c>
       <c r="J5" s="2">
         <v>3</v>
@@ -731,10 +683,10 @@
         <v>5</v>
       </c>
       <c r="N5" s="2">
-        <v>4.75</v>
+        <v>14.25</v>
       </c>
       <c r="O5" s="2" t="s">
-        <v>45</v>
+        <v>28</v>
       </c>
       <c r="P5" s="2" t="s">
         <v>0</v>
@@ -745,19 +697,19 @@
         <v>2</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>44</v>
+        <v>27</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>43</v>
+        <v>26</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>42</v>
+        <v>25</v>
       </c>
       <c r="E6" s="2" t="s">
         <v>3</v>
       </c>
       <c r="F6" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G6" s="2">
         <v>10.0</v>
@@ -766,7 +718,7 @@
         <v>10.0</v>
       </c>
       <c r="I6" s="2" t="s">
-        <v>17</v>
+        <v>2</v>
       </c>
       <c r="J6" s="2">
         <v>5</v>
@@ -777,10 +729,10 @@
         <v>5</v>
       </c>
       <c r="N6" s="2">
-        <v>4.35</v>
+        <v>3.77</v>
       </c>
       <c r="O6" s="2" t="s">
-        <v>41</v>
+        <v>24</v>
       </c>
       <c r="P6" s="2" t="s">
         <v>0</v>
@@ -791,13 +743,13 @@
         <v>3</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>40</v>
+        <v>23</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>39</v>
+        <v>22</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>38</v>
+        <v>21</v>
       </c>
       <c r="E7" s="2" t="s">
         <v>3</v>
@@ -812,7 +764,7 @@
         <v>10.0</v>
       </c>
       <c r="I7" s="2" t="s">
-        <v>17</v>
+        <v>2</v>
       </c>
       <c r="J7" s="2">
         <v>5</v>
@@ -823,10 +775,10 @@
         <v>5</v>
       </c>
       <c r="N7" s="2">
-        <v>4.57</v>
+        <v>5.62</v>
       </c>
       <c r="O7" s="2" t="s">
-        <v>37</v>
+        <v>20</v>
       </c>
       <c r="P7" s="2" t="s">
         <v>0</v>
@@ -837,13 +789,13 @@
         <v>4</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>36</v>
+        <v>19</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>35</v>
+        <v>18</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>34</v>
+        <v>17</v>
       </c>
       <c r="E8" s="2" t="s">
         <v>3</v>
@@ -852,27 +804,29 @@
         <v>1</v>
       </c>
       <c r="G8" s="2">
-        <v>10.0</v>
+        <v>8.0</v>
       </c>
       <c r="H8" s="2">
         <v>10.0</v>
       </c>
       <c r="I8" s="2" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="J8" s="2">
-        <v>5</v>
-      </c>
-      <c r="K8" s="2"/>
+        <v>4</v>
+      </c>
+      <c r="K8" s="2">
+        <v>1</v>
+      </c>
       <c r="L8" s="2"/>
       <c r="M8" s="2">
         <v>5</v>
       </c>
       <c r="N8" s="2">
-        <v>2.07</v>
+        <v>29.93</v>
       </c>
       <c r="O8" s="2" t="s">
-        <v>33</v>
+        <v>16</v>
       </c>
       <c r="P8" s="2" t="s">
         <v>0</v>
@@ -883,19 +837,19 @@
         <v>5</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>32</v>
+        <v>15</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>31</v>
+        <v>14</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>30</v>
+        <v>13</v>
       </c>
       <c r="E9" s="2" t="s">
         <v>3</v>
       </c>
       <c r="F9" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G9" s="2">
         <v>8.0</v>
@@ -904,7 +858,7 @@
         <v>10.0</v>
       </c>
       <c r="I9" s="2" t="s">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="J9" s="2">
         <v>4</v>
@@ -917,10 +871,10 @@
         <v>5</v>
       </c>
       <c r="N9" s="2">
-        <v>12.95</v>
+        <v>69.77</v>
       </c>
       <c r="O9" s="2" t="s">
-        <v>29</v>
+        <v>11</v>
       </c>
       <c r="P9" s="2" t="s">
         <v>0</v>
@@ -931,13 +885,13 @@
         <v>6</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>28</v>
+        <v>10</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>27</v>
+        <v>9</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>26</v>
+        <v>8</v>
       </c>
       <c r="E10" s="2" t="s">
         <v>3</v>
@@ -946,7 +900,7 @@
         <v>1</v>
       </c>
       <c r="G10" s="2">
-        <v>8.0</v>
+        <v>10.0</v>
       </c>
       <c r="H10" s="2">
         <v>10.0</v>
@@ -955,20 +909,18 @@
         <v>2</v>
       </c>
       <c r="J10" s="2">
-        <v>4</v>
-      </c>
-      <c r="K10" s="2">
-        <v>1</v>
-      </c>
+        <v>5</v>
+      </c>
+      <c r="K10" s="2"/>
       <c r="L10" s="2"/>
       <c r="M10" s="2">
         <v>5</v>
       </c>
       <c r="N10" s="2">
-        <v>3.87</v>
+        <v>20.27</v>
       </c>
       <c r="O10" s="2" t="s">
-        <v>25</v>
+        <v>7</v>
       </c>
       <c r="P10" s="2" t="s">
         <v>0</v>
@@ -979,22 +931,22 @@
         <v>7</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>24</v>
+        <v>6</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>23</v>
+        <v>5</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>22</v>
+        <v>4</v>
       </c>
       <c r="E11" s="2" t="s">
         <v>3</v>
       </c>
       <c r="F11" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G11" s="2">
-        <v>8.0</v>
+        <v>10.0</v>
       </c>
       <c r="H11" s="2">
         <v>10.0</v>
@@ -1003,212 +955,20 @@
         <v>2</v>
       </c>
       <c r="J11" s="2">
-        <v>4</v>
-      </c>
-      <c r="K11" s="2">
-        <v>1</v>
-      </c>
+        <v>5</v>
+      </c>
+      <c r="K11" s="2"/>
       <c r="L11" s="2"/>
       <c r="M11" s="2">
         <v>5</v>
       </c>
       <c r="N11" s="2">
-        <v>16.37</v>
+        <v>21.33</v>
       </c>
       <c r="O11" s="2" t="s">
-        <v>21</v>
+        <v>1</v>
       </c>
       <c r="P11" s="2" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="12" spans="1:16">
-      <c r="A12" s="2">
-        <v>8</v>
-      </c>
-      <c r="B12" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="C12" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="D12" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="E12" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="F12" s="2">
-        <v>1</v>
-      </c>
-      <c r="G12" s="2">
-        <v>10.0</v>
-      </c>
-      <c r="H12" s="2">
-        <v>10.0</v>
-      </c>
-      <c r="I12" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="J12" s="2">
-        <v>5</v>
-      </c>
-      <c r="K12" s="2"/>
-      <c r="L12" s="2"/>
-      <c r="M12" s="2">
-        <v>5</v>
-      </c>
-      <c r="N12" s="2">
-        <v>9.97</v>
-      </c>
-      <c r="O12" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="P12" s="2" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="13" spans="1:16">
-      <c r="A13" s="2">
-        <v>9</v>
-      </c>
-      <c r="B13" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="C13" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="D13" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="E13" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="F13" s="2">
-        <v>1</v>
-      </c>
-      <c r="G13" s="2">
-        <v>6.0</v>
-      </c>
-      <c r="H13" s="2">
-        <v>10.0</v>
-      </c>
-      <c r="I13" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="J13" s="2">
-        <v>3</v>
-      </c>
-      <c r="K13" s="2">
-        <v>2</v>
-      </c>
-      <c r="L13" s="2"/>
-      <c r="M13" s="2">
-        <v>5</v>
-      </c>
-      <c r="N13" s="2">
-        <v>7.03</v>
-      </c>
-      <c r="O13" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="P13" s="2" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="14" spans="1:16">
-      <c r="A14" s="2">
-        <v>10</v>
-      </c>
-      <c r="B14" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="C14" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="D14" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="E14" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="F14" s="2">
-        <v>1</v>
-      </c>
-      <c r="G14" s="2">
-        <v>6.0</v>
-      </c>
-      <c r="H14" s="2">
-        <v>10.0</v>
-      </c>
-      <c r="I14" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="J14" s="2">
-        <v>3</v>
-      </c>
-      <c r="K14" s="2">
-        <v>2</v>
-      </c>
-      <c r="L14" s="2"/>
-      <c r="M14" s="2">
-        <v>5</v>
-      </c>
-      <c r="N14" s="2">
-        <v>31.33</v>
-      </c>
-      <c r="O14" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="P14" s="2" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15" spans="1:16">
-      <c r="A15" s="2">
-        <v>11</v>
-      </c>
-      <c r="B15" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="C15" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="D15" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="E15" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="F15" s="2">
-        <v>1</v>
-      </c>
-      <c r="G15" s="2">
-        <v>8.0</v>
-      </c>
-      <c r="H15" s="2">
-        <v>10.0</v>
-      </c>
-      <c r="I15" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="J15" s="2">
-        <v>4</v>
-      </c>
-      <c r="K15" s="2">
-        <v>1</v>
-      </c>
-      <c r="L15" s="2"/>
-      <c r="M15" s="2">
-        <v>5</v>
-      </c>
-      <c r="N15" s="2">
-        <v>4.08</v>
-      </c>
-      <c r="O15" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="P15" s="2" t="s">
         <v>0</v>
       </c>
     </row>

--- a/2lit_online.xlsx
+++ b/2lit_online.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="52">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="60">
   <si>
     <t>ناجح ✓</t>
   </si>
@@ -116,6 +116,30 @@
     <t>Malak Hassan</t>
   </si>
   <si>
+    <t>2026-03-15 23:36</t>
+  </si>
+  <si>
+    <t>01115527889</t>
+  </si>
+  <si>
+    <t>Lomasalma@icloud.com</t>
+  </si>
+  <si>
+    <t>سلمي اشرف عبدالحيم علي</t>
+  </si>
+  <si>
+    <t>2026-03-16 12:47</t>
+  </si>
+  <si>
+    <t>01090635624</t>
+  </si>
+  <si>
+    <t>yasser1062008@gmail.com</t>
+  </si>
+  <si>
+    <t>Yasser Mohamed fayez</t>
+  </si>
+  <si>
     <t>الحالة</t>
   </si>
   <si>
@@ -170,7 +194,7 @@
     <t>الدرجة الكاملة: 10 | درجة النجاح: 5.00</t>
   </si>
   <si>
-    <t>تاريخ التصدير: 2026-03-15 19:18</t>
+    <t>تاريخ التصدير: 2026-03-16 19:31</t>
   </si>
 </sst>
 </file>
@@ -558,7 +582,7 @@
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
   </sheetPr>
-  <dimension ref="A1:P11"/>
+  <dimension ref="A1:P13"/>
   <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col min="1" max="1" width="6" customWidth="true" style="0"/>
@@ -581,67 +605,67 @@
   <sheetData>
     <row r="1" spans="1:16">
       <c r="A1" s="3" t="s">
-        <v>49</v>
+        <v>57</v>
       </c>
     </row>
     <row r="2" spans="1:16">
       <c r="A2" s="3" t="s">
-        <v>50</v>
+        <v>58</v>
       </c>
     </row>
     <row r="3" spans="1:16">
       <c r="A3" s="3" t="s">
-        <v>51</v>
+        <v>59</v>
       </c>
     </row>
     <row r="4" spans="1:16">
       <c r="A4" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="E4" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="F4" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="G4" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="H4" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="I4" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="B4" s="1" t="s">
+      <c r="J4" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="C4" s="1" t="s">
+      <c r="K4" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="D4" s="1" t="s">
+      <c r="L4" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="E4" s="1" t="s">
+      <c r="M4" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="F4" s="1" t="s">
+      <c r="N4" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="G4" s="1" t="s">
+      <c r="O4" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="H4" s="1" t="s">
+      <c r="P4" s="1" t="s">
         <v>41</v>
-      </c>
-      <c r="I4" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="J4" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="K4" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="L4" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="M4" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="N4" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="O4" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="P4" s="1" t="s">
-        <v>33</v>
       </c>
     </row>
     <row r="5" spans="1:16">
@@ -649,13 +673,13 @@
         <v>1</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>32</v>
+        <v>40</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>31</v>
+        <v>39</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>30</v>
+        <v>38</v>
       </c>
       <c r="E5" s="2" t="s">
         <v>3</v>
@@ -664,29 +688,29 @@
         <v>1</v>
       </c>
       <c r="G5" s="2">
-        <v>6.0</v>
+        <v>8.0</v>
       </c>
       <c r="H5" s="2">
         <v>10.0</v>
       </c>
       <c r="I5" s="2" t="s">
-        <v>29</v>
+        <v>12</v>
       </c>
       <c r="J5" s="2">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K5" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L5" s="2"/>
       <c r="M5" s="2">
         <v>5</v>
       </c>
       <c r="N5" s="2">
-        <v>14.25</v>
+        <v>14.27</v>
       </c>
       <c r="O5" s="2" t="s">
-        <v>28</v>
+        <v>37</v>
       </c>
       <c r="P5" s="2" t="s">
         <v>0</v>
@@ -697,13 +721,13 @@
         <v>2</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>27</v>
+        <v>36</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>26</v>
+        <v>35</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>25</v>
+        <v>34</v>
       </c>
       <c r="E6" s="2" t="s">
         <v>3</v>
@@ -712,27 +736,29 @@
         <v>2</v>
       </c>
       <c r="G6" s="2">
-        <v>10.0</v>
+        <v>6.0</v>
       </c>
       <c r="H6" s="2">
         <v>10.0</v>
       </c>
       <c r="I6" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="J6" s="2">
+        <v>3</v>
+      </c>
+      <c r="K6" s="2">
         <v>2</v>
       </c>
-      <c r="J6" s="2">
-        <v>5</v>
-      </c>
-      <c r="K6" s="2"/>
       <c r="L6" s="2"/>
       <c r="M6" s="2">
         <v>5</v>
       </c>
       <c r="N6" s="2">
-        <v>3.77</v>
+        <v>1.62</v>
       </c>
       <c r="O6" s="2" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
       <c r="P6" s="2" t="s">
         <v>0</v>
@@ -743,13 +769,13 @@
         <v>3</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>23</v>
+        <v>32</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>22</v>
+        <v>31</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>21</v>
+        <v>30</v>
       </c>
       <c r="E7" s="2" t="s">
         <v>3</v>
@@ -758,27 +784,29 @@
         <v>1</v>
       </c>
       <c r="G7" s="2">
-        <v>10.0</v>
+        <v>6.0</v>
       </c>
       <c r="H7" s="2">
         <v>10.0</v>
       </c>
       <c r="I7" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="J7" s="2">
+        <v>3</v>
+      </c>
+      <c r="K7" s="2">
         <v>2</v>
       </c>
-      <c r="J7" s="2">
-        <v>5</v>
-      </c>
-      <c r="K7" s="2"/>
       <c r="L7" s="2"/>
       <c r="M7" s="2">
         <v>5</v>
       </c>
       <c r="N7" s="2">
-        <v>5.62</v>
+        <v>14.25</v>
       </c>
       <c r="O7" s="2" t="s">
-        <v>20</v>
+        <v>28</v>
       </c>
       <c r="P7" s="2" t="s">
         <v>0</v>
@@ -789,44 +817,42 @@
         <v>4</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>19</v>
+        <v>27</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>18</v>
+        <v>26</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="E8" s="2" t="s">
         <v>3</v>
       </c>
       <c r="F8" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G8" s="2">
-        <v>8.0</v>
+        <v>10.0</v>
       </c>
       <c r="H8" s="2">
         <v>10.0</v>
       </c>
       <c r="I8" s="2" t="s">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="J8" s="2">
-        <v>4</v>
-      </c>
-      <c r="K8" s="2">
-        <v>1</v>
-      </c>
+        <v>5</v>
+      </c>
+      <c r="K8" s="2"/>
       <c r="L8" s="2"/>
       <c r="M8" s="2">
         <v>5</v>
       </c>
       <c r="N8" s="2">
-        <v>29.93</v>
+        <v>3.77</v>
       </c>
       <c r="O8" s="2" t="s">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="P8" s="2" t="s">
         <v>0</v>
@@ -837,44 +863,42 @@
         <v>5</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="E9" s="2" t="s">
         <v>3</v>
       </c>
       <c r="F9" s="2">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G9" s="2">
-        <v>8.0</v>
+        <v>10.0</v>
       </c>
       <c r="H9" s="2">
         <v>10.0</v>
       </c>
       <c r="I9" s="2" t="s">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="J9" s="2">
-        <v>4</v>
-      </c>
-      <c r="K9" s="2">
-        <v>1</v>
-      </c>
+        <v>5</v>
+      </c>
+      <c r="K9" s="2"/>
       <c r="L9" s="2"/>
       <c r="M9" s="2">
         <v>5</v>
       </c>
       <c r="N9" s="2">
-        <v>69.77</v>
+        <v>5.62</v>
       </c>
       <c r="O9" s="2" t="s">
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="P9" s="2" t="s">
         <v>0</v>
@@ -885,13 +909,13 @@
         <v>6</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>9</v>
+        <v>18</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="E10" s="2" t="s">
         <v>3</v>
@@ -900,27 +924,29 @@
         <v>1</v>
       </c>
       <c r="G10" s="2">
-        <v>10.0</v>
+        <v>8.0</v>
       </c>
       <c r="H10" s="2">
         <v>10.0</v>
       </c>
       <c r="I10" s="2" t="s">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="J10" s="2">
-        <v>5</v>
-      </c>
-      <c r="K10" s="2"/>
+        <v>4</v>
+      </c>
+      <c r="K10" s="2">
+        <v>1</v>
+      </c>
       <c r="L10" s="2"/>
       <c r="M10" s="2">
         <v>5</v>
       </c>
       <c r="N10" s="2">
-        <v>20.27</v>
+        <v>29.93</v>
       </c>
       <c r="O10" s="2" t="s">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="P10" s="2" t="s">
         <v>0</v>
@@ -931,44 +957,138 @@
         <v>7</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="D11" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="E11" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="F11" s="2">
+        <v>3</v>
+      </c>
+      <c r="G11" s="2">
+        <v>8.0</v>
+      </c>
+      <c r="H11" s="2">
+        <v>10.0</v>
+      </c>
+      <c r="I11" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="J11" s="2">
         <v>4</v>
       </c>
-      <c r="E11" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="F11" s="2">
+      <c r="K11" s="2">
         <v>1</v>
       </c>
-      <c r="G11" s="2">
-        <v>10.0</v>
-      </c>
-      <c r="H11" s="2">
-        <v>10.0</v>
-      </c>
-      <c r="I11" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="J11" s="2">
-        <v>5</v>
-      </c>
-      <c r="K11" s="2"/>
       <c r="L11" s="2"/>
       <c r="M11" s="2">
         <v>5</v>
       </c>
       <c r="N11" s="2">
+        <v>69.77</v>
+      </c>
+      <c r="O11" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="P11" s="2" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:16">
+      <c r="A12" s="2">
+        <v>8</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="C12" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D12" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E12" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="F12" s="2">
+        <v>1</v>
+      </c>
+      <c r="G12" s="2">
+        <v>10.0</v>
+      </c>
+      <c r="H12" s="2">
+        <v>10.0</v>
+      </c>
+      <c r="I12" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="J12" s="2">
+        <v>5</v>
+      </c>
+      <c r="K12" s="2"/>
+      <c r="L12" s="2"/>
+      <c r="M12" s="2">
+        <v>5</v>
+      </c>
+      <c r="N12" s="2">
+        <v>20.27</v>
+      </c>
+      <c r="O12" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="P12" s="2" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:16">
+      <c r="A13" s="2">
+        <v>9</v>
+      </c>
+      <c r="B13" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="C13" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="D13" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="E13" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="F13" s="2">
+        <v>1</v>
+      </c>
+      <c r="G13" s="2">
+        <v>10.0</v>
+      </c>
+      <c r="H13" s="2">
+        <v>10.0</v>
+      </c>
+      <c r="I13" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="J13" s="2">
+        <v>5</v>
+      </c>
+      <c r="K13" s="2"/>
+      <c r="L13" s="2"/>
+      <c r="M13" s="2">
+        <v>5</v>
+      </c>
+      <c r="N13" s="2">
         <v>21.33</v>
       </c>
-      <c r="O11" s="2" t="s">
+      <c r="O13" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="P11" s="2" t="s">
+      <c r="P13" s="2" t="s">
         <v>0</v>
       </c>
     </row>

--- a/2lit_online.xlsx
+++ b/2lit_online.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="60">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="112">
   <si>
     <t>ناجح ✓</t>
   </si>
@@ -140,6 +140,162 @@
     <t>Yasser Mohamed fayez</t>
   </si>
   <si>
+    <t>2026-03-17 14:25</t>
+  </si>
+  <si>
+    <t>01229920604</t>
+  </si>
+  <si>
+    <t>hanyyyfadyyy9@gmail.com</t>
+  </si>
+  <si>
+    <t>فادي هاني مكرم</t>
+  </si>
+  <si>
+    <t>2026-03-18 22:11</t>
+  </si>
+  <si>
+    <t>01014788879</t>
+  </si>
+  <si>
+    <t>roaamohammed1752009@gmailcom</t>
+  </si>
+  <si>
+    <t>Roaa Mohammed hemeida galal</t>
+  </si>
+  <si>
+    <t>2026-03-21 02:30</t>
+  </si>
+  <si>
+    <t>01204338071</t>
+  </si>
+  <si>
+    <t>mariamkhaled121aa@gmail.com</t>
+  </si>
+  <si>
+    <t>OMariam Khaled</t>
+  </si>
+  <si>
+    <t>2026-03-21 22:59</t>
+  </si>
+  <si>
+    <t>01120749269</t>
+  </si>
+  <si>
+    <t>rokayaelsawy8@gmail.com</t>
+  </si>
+  <si>
+    <t>Rokaya Elsawy</t>
+  </si>
+  <si>
+    <t>2026-03-23 12:28</t>
+  </si>
+  <si>
+    <t>01030078898</t>
+  </si>
+  <si>
+    <t>nodyfahmy2010@gmail.com</t>
+  </si>
+  <si>
+    <t>Nada Ahmed</t>
+  </si>
+  <si>
+    <t>2026-03-23 19:15</t>
+  </si>
+  <si>
+    <t>01551501457</t>
+  </si>
+  <si>
+    <t>roaaahmed21080001@gmail.com</t>
+  </si>
+  <si>
+    <t>رؤى احمد حسين</t>
+  </si>
+  <si>
+    <t>2026-03-24 12:59</t>
+  </si>
+  <si>
+    <t>01225663353</t>
+  </si>
+  <si>
+    <t>tonymichel3030@gmail.com</t>
+  </si>
+  <si>
+    <t>Tony michel alfy</t>
+  </si>
+  <si>
+    <t>2026-03-24 21:22</t>
+  </si>
+  <si>
+    <t>01013657697</t>
+  </si>
+  <si>
+    <t>reemreda1022010@gmail.com</t>
+  </si>
+  <si>
+    <t>reem reda Mohamed</t>
+  </si>
+  <si>
+    <t>2026-03-25 14:41</t>
+  </si>
+  <si>
+    <t>01090829109</t>
+  </si>
+  <si>
+    <t>Mylittleponymm431@gmail.com</t>
+  </si>
+  <si>
+    <t>Mariam Mo3taz Mohamed</t>
+  </si>
+  <si>
+    <t>2026-03-26 21:58</t>
+  </si>
+  <si>
+    <t>01148353989</t>
+  </si>
+  <si>
+    <t>janaamrmohamed2472009@gmail.com</t>
+  </si>
+  <si>
+    <t>Jana Amr</t>
+  </si>
+  <si>
+    <t>2026-03-26 22:31</t>
+  </si>
+  <si>
+    <t>01064649220</t>
+  </si>
+  <si>
+    <t>Moharoon663@gmail.com</t>
+  </si>
+  <si>
+    <t>Mohamed omar</t>
+  </si>
+  <si>
+    <t>2026-03-27 12:55</t>
+  </si>
+  <si>
+    <t>01023678107</t>
+  </si>
+  <si>
+    <t>malk1662008@gmail.com</t>
+  </si>
+  <si>
+    <t>Malak Ahmed Aboubakr</t>
+  </si>
+  <si>
+    <t>2026-03-29 15:50</t>
+  </si>
+  <si>
+    <t>01027709112</t>
+  </si>
+  <si>
+    <t>tasneemabdelnasser0@gmail.com</t>
+  </si>
+  <si>
+    <t>Tasneem abdelnasser</t>
+  </si>
+  <si>
     <t>الحالة</t>
   </si>
   <si>
@@ -194,7 +350,7 @@
     <t>الدرجة الكاملة: 10 | درجة النجاح: 5.00</t>
   </si>
   <si>
-    <t>تاريخ التصدير: 2026-03-16 19:31</t>
+    <t>تاريخ التصدير: 2026-03-29 16:33</t>
   </si>
 </sst>
 </file>
@@ -582,7 +738,7 @@
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
   </sheetPr>
-  <dimension ref="A1:P13"/>
+  <dimension ref="A1:P26"/>
   <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col min="1" max="1" width="6" customWidth="true" style="0"/>
@@ -605,67 +761,67 @@
   <sheetData>
     <row r="1" spans="1:16">
       <c r="A1" s="3" t="s">
-        <v>57</v>
+        <v>109</v>
       </c>
     </row>
     <row r="2" spans="1:16">
       <c r="A2" s="3" t="s">
-        <v>58</v>
+        <v>110</v>
       </c>
     </row>
     <row r="3" spans="1:16">
       <c r="A3" s="3" t="s">
-        <v>59</v>
+        <v>111</v>
       </c>
     </row>
     <row r="4" spans="1:16">
       <c r="A4" s="1" t="s">
-        <v>56</v>
+        <v>108</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>55</v>
+        <v>107</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>54</v>
+        <v>106</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>53</v>
+        <v>105</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>52</v>
+        <v>104</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>51</v>
+        <v>103</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>50</v>
+        <v>102</v>
       </c>
       <c r="H4" s="1" t="s">
-        <v>49</v>
+        <v>101</v>
       </c>
       <c r="I4" s="1" t="s">
-        <v>48</v>
+        <v>100</v>
       </c>
       <c r="J4" s="1" t="s">
-        <v>47</v>
+        <v>99</v>
       </c>
       <c r="K4" s="1" t="s">
-        <v>46</v>
+        <v>98</v>
       </c>
       <c r="L4" s="1" t="s">
-        <v>45</v>
+        <v>97</v>
       </c>
       <c r="M4" s="1" t="s">
-        <v>44</v>
+        <v>96</v>
       </c>
       <c r="N4" s="1" t="s">
-        <v>43</v>
+        <v>95</v>
       </c>
       <c r="O4" s="1" t="s">
-        <v>42</v>
+        <v>94</v>
       </c>
       <c r="P4" s="1" t="s">
-        <v>41</v>
+        <v>93</v>
       </c>
     </row>
     <row r="5" spans="1:16">
@@ -673,13 +829,13 @@
         <v>1</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>40</v>
+        <v>92</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>39</v>
+        <v>91</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>38</v>
+        <v>90</v>
       </c>
       <c r="E5" s="2" t="s">
         <v>3</v>
@@ -688,29 +844,27 @@
         <v>1</v>
       </c>
       <c r="G5" s="2">
-        <v>8.0</v>
+        <v>10.0</v>
       </c>
       <c r="H5" s="2">
         <v>10.0</v>
       </c>
       <c r="I5" s="2" t="s">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="J5" s="2">
-        <v>4</v>
-      </c>
-      <c r="K5" s="2">
-        <v>1</v>
-      </c>
+        <v>5</v>
+      </c>
+      <c r="K5" s="2"/>
       <c r="L5" s="2"/>
       <c r="M5" s="2">
         <v>5</v>
       </c>
       <c r="N5" s="2">
-        <v>14.27</v>
+        <v>20.67</v>
       </c>
       <c r="O5" s="2" t="s">
-        <v>37</v>
+        <v>89</v>
       </c>
       <c r="P5" s="2" t="s">
         <v>0</v>
@@ -721,44 +875,42 @@
         <v>2</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>36</v>
+        <v>88</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>35</v>
+        <v>87</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>34</v>
+        <v>86</v>
       </c>
       <c r="E6" s="2" t="s">
         <v>3</v>
       </c>
       <c r="F6" s="2">
+        <v>1</v>
+      </c>
+      <c r="G6" s="2">
+        <v>10.0</v>
+      </c>
+      <c r="H6" s="2">
+        <v>10.0</v>
+      </c>
+      <c r="I6" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="G6" s="2">
-        <v>6.0</v>
-      </c>
-      <c r="H6" s="2">
-        <v>10.0</v>
-      </c>
-      <c r="I6" s="2" t="s">
-        <v>29</v>
-      </c>
       <c r="J6" s="2">
-        <v>3</v>
-      </c>
-      <c r="K6" s="2">
-        <v>2</v>
-      </c>
+        <v>5</v>
+      </c>
+      <c r="K6" s="2"/>
       <c r="L6" s="2"/>
       <c r="M6" s="2">
         <v>5</v>
       </c>
       <c r="N6" s="2">
-        <v>1.62</v>
+        <v>10.48</v>
       </c>
       <c r="O6" s="2" t="s">
-        <v>33</v>
+        <v>85</v>
       </c>
       <c r="P6" s="2" t="s">
         <v>0</v>
@@ -769,13 +921,13 @@
         <v>3</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>32</v>
+        <v>84</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>31</v>
+        <v>83</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>30</v>
+        <v>82</v>
       </c>
       <c r="E7" s="2" t="s">
         <v>3</v>
@@ -784,29 +936,27 @@
         <v>1</v>
       </c>
       <c r="G7" s="2">
-        <v>6.0</v>
+        <v>10.0</v>
       </c>
       <c r="H7" s="2">
         <v>10.0</v>
       </c>
       <c r="I7" s="2" t="s">
-        <v>29</v>
+        <v>2</v>
       </c>
       <c r="J7" s="2">
-        <v>3</v>
-      </c>
-      <c r="K7" s="2">
-        <v>2</v>
-      </c>
+        <v>5</v>
+      </c>
+      <c r="K7" s="2"/>
       <c r="L7" s="2"/>
       <c r="M7" s="2">
         <v>5</v>
       </c>
       <c r="N7" s="2">
-        <v>14.25</v>
+        <v>2.65</v>
       </c>
       <c r="O7" s="2" t="s">
-        <v>28</v>
+        <v>81</v>
       </c>
       <c r="P7" s="2" t="s">
         <v>0</v>
@@ -817,19 +967,19 @@
         <v>4</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>27</v>
+        <v>80</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>26</v>
+        <v>79</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>25</v>
+        <v>78</v>
       </c>
       <c r="E8" s="2" t="s">
         <v>3</v>
       </c>
       <c r="F8" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G8" s="2">
         <v>10.0</v>
@@ -849,10 +999,10 @@
         <v>5</v>
       </c>
       <c r="N8" s="2">
-        <v>3.77</v>
+        <v>11.3</v>
       </c>
       <c r="O8" s="2" t="s">
-        <v>24</v>
+        <v>77</v>
       </c>
       <c r="P8" s="2" t="s">
         <v>0</v>
@@ -863,13 +1013,13 @@
         <v>5</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>23</v>
+        <v>76</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>22</v>
+        <v>75</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>21</v>
+        <v>74</v>
       </c>
       <c r="E9" s="2" t="s">
         <v>3</v>
@@ -895,10 +1045,10 @@
         <v>5</v>
       </c>
       <c r="N9" s="2">
-        <v>5.62</v>
+        <v>11.27</v>
       </c>
       <c r="O9" s="2" t="s">
-        <v>20</v>
+        <v>73</v>
       </c>
       <c r="P9" s="2" t="s">
         <v>0</v>
@@ -909,13 +1059,13 @@
         <v>6</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>19</v>
+        <v>72</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>18</v>
+        <v>71</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>17</v>
+        <v>70</v>
       </c>
       <c r="E10" s="2" t="s">
         <v>3</v>
@@ -943,10 +1093,10 @@
         <v>5</v>
       </c>
       <c r="N10" s="2">
-        <v>29.93</v>
+        <v>7.5</v>
       </c>
       <c r="O10" s="2" t="s">
-        <v>16</v>
+        <v>69</v>
       </c>
       <c r="P10" s="2" t="s">
         <v>0</v>
@@ -957,44 +1107,42 @@
         <v>7</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>15</v>
+        <v>68</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>14</v>
+        <v>67</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>13</v>
+        <v>66</v>
       </c>
       <c r="E11" s="2" t="s">
         <v>3</v>
       </c>
       <c r="F11" s="2">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G11" s="2">
-        <v>8.0</v>
+        <v>10.0</v>
       </c>
       <c r="H11" s="2">
         <v>10.0</v>
       </c>
       <c r="I11" s="2" t="s">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="J11" s="2">
-        <v>4</v>
-      </c>
-      <c r="K11" s="2">
-        <v>1</v>
-      </c>
+        <v>5</v>
+      </c>
+      <c r="K11" s="2"/>
       <c r="L11" s="2"/>
       <c r="M11" s="2">
         <v>5</v>
       </c>
       <c r="N11" s="2">
-        <v>69.77</v>
+        <v>5.17</v>
       </c>
       <c r="O11" s="2" t="s">
-        <v>11</v>
+        <v>65</v>
       </c>
       <c r="P11" s="2" t="s">
         <v>0</v>
@@ -1005,13 +1153,13 @@
         <v>8</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>10</v>
+        <v>64</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>9</v>
+        <v>63</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>8</v>
+        <v>62</v>
       </c>
       <c r="E12" s="2" t="s">
         <v>3</v>
@@ -1020,27 +1168,29 @@
         <v>1</v>
       </c>
       <c r="G12" s="2">
-        <v>10.0</v>
+        <v>8.0</v>
       </c>
       <c r="H12" s="2">
         <v>10.0</v>
       </c>
       <c r="I12" s="2" t="s">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="J12" s="2">
-        <v>5</v>
-      </c>
-      <c r="K12" s="2"/>
+        <v>4</v>
+      </c>
+      <c r="K12" s="2">
+        <v>1</v>
+      </c>
       <c r="L12" s="2"/>
       <c r="M12" s="2">
         <v>5</v>
       </c>
       <c r="N12" s="2">
-        <v>20.27</v>
+        <v>10.48</v>
       </c>
       <c r="O12" s="2" t="s">
-        <v>7</v>
+        <v>61</v>
       </c>
       <c r="P12" s="2" t="s">
         <v>0</v>
@@ -1051,44 +1201,654 @@
         <v>9</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>6</v>
+        <v>60</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>5</v>
+        <v>59</v>
       </c>
       <c r="D13" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="E13" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="F13" s="2">
+        <v>1</v>
+      </c>
+      <c r="G13" s="2">
+        <v>8.0</v>
+      </c>
+      <c r="H13" s="2">
+        <v>10.0</v>
+      </c>
+      <c r="I13" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="J13" s="2">
         <v>4</v>
       </c>
-      <c r="E13" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="F13" s="2">
-        <v>1</v>
-      </c>
-      <c r="G13" s="2">
-        <v>10.0</v>
-      </c>
-      <c r="H13" s="2">
-        <v>10.0</v>
-      </c>
-      <c r="I13" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="J13" s="2">
-        <v>5</v>
-      </c>
-      <c r="K13" s="2"/>
+      <c r="K13" s="2">
+        <v>1</v>
+      </c>
       <c r="L13" s="2"/>
       <c r="M13" s="2">
         <v>5</v>
       </c>
       <c r="N13" s="2">
+        <v>29.6</v>
+      </c>
+      <c r="O13" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="P13" s="2" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:16">
+      <c r="A14" s="2">
+        <v>10</v>
+      </c>
+      <c r="B14" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="C14" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="D14" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="E14" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="F14" s="2">
+        <v>1</v>
+      </c>
+      <c r="G14" s="2">
+        <v>10.0</v>
+      </c>
+      <c r="H14" s="2">
+        <v>10.0</v>
+      </c>
+      <c r="I14" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="J14" s="2">
+        <v>5</v>
+      </c>
+      <c r="K14" s="2"/>
+      <c r="L14" s="2"/>
+      <c r="M14" s="2">
+        <v>5</v>
+      </c>
+      <c r="N14" s="2">
+        <v>4.43</v>
+      </c>
+      <c r="O14" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="P14" s="2" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:16">
+      <c r="A15" s="2">
+        <v>11</v>
+      </c>
+      <c r="B15" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="C15" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="D15" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="E15" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="F15" s="2">
+        <v>1</v>
+      </c>
+      <c r="G15" s="2">
+        <v>10.0</v>
+      </c>
+      <c r="H15" s="2">
+        <v>10.0</v>
+      </c>
+      <c r="I15" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="J15" s="2">
+        <v>5</v>
+      </c>
+      <c r="K15" s="2"/>
+      <c r="L15" s="2"/>
+      <c r="M15" s="2">
+        <v>5</v>
+      </c>
+      <c r="N15" s="2">
+        <v>7.9</v>
+      </c>
+      <c r="O15" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="P15" s="2" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:16">
+      <c r="A16" s="2">
+        <v>12</v>
+      </c>
+      <c r="B16" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="C16" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="D16" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="E16" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="F16" s="2">
+        <v>1</v>
+      </c>
+      <c r="G16" s="2">
+        <v>10.0</v>
+      </c>
+      <c r="H16" s="2">
+        <v>10.0</v>
+      </c>
+      <c r="I16" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="J16" s="2">
+        <v>5</v>
+      </c>
+      <c r="K16" s="2"/>
+      <c r="L16" s="2"/>
+      <c r="M16" s="2">
+        <v>5</v>
+      </c>
+      <c r="N16" s="2">
+        <v>12.17</v>
+      </c>
+      <c r="O16" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="P16" s="2" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="1:16">
+      <c r="A17" s="2">
+        <v>13</v>
+      </c>
+      <c r="B17" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="C17" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="D17" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="E17" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="F17" s="2">
+        <v>1</v>
+      </c>
+      <c r="G17" s="2">
+        <v>10.0</v>
+      </c>
+      <c r="H17" s="2">
+        <v>10.0</v>
+      </c>
+      <c r="I17" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="J17" s="2">
+        <v>5</v>
+      </c>
+      <c r="K17" s="2"/>
+      <c r="L17" s="2"/>
+      <c r="M17" s="2">
+        <v>5</v>
+      </c>
+      <c r="N17" s="2">
+        <v>2.65</v>
+      </c>
+      <c r="O17" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="P17" s="2" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="1:16">
+      <c r="A18" s="2">
+        <v>14</v>
+      </c>
+      <c r="B18" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="C18" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="D18" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="E18" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="F18" s="2">
+        <v>1</v>
+      </c>
+      <c r="G18" s="2">
+        <v>8.0</v>
+      </c>
+      <c r="H18" s="2">
+        <v>10.0</v>
+      </c>
+      <c r="I18" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="J18" s="2">
+        <v>4</v>
+      </c>
+      <c r="K18" s="2">
+        <v>1</v>
+      </c>
+      <c r="L18" s="2"/>
+      <c r="M18" s="2">
+        <v>5</v>
+      </c>
+      <c r="N18" s="2">
+        <v>14.27</v>
+      </c>
+      <c r="O18" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="P18" s="2" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="1:16">
+      <c r="A19" s="2">
+        <v>15</v>
+      </c>
+      <c r="B19" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="C19" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="D19" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="E19" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="F19" s="2">
+        <v>2</v>
+      </c>
+      <c r="G19" s="2">
+        <v>6.0</v>
+      </c>
+      <c r="H19" s="2">
+        <v>10.0</v>
+      </c>
+      <c r="I19" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="J19" s="2">
+        <v>3</v>
+      </c>
+      <c r="K19" s="2">
+        <v>2</v>
+      </c>
+      <c r="L19" s="2"/>
+      <c r="M19" s="2">
+        <v>5</v>
+      </c>
+      <c r="N19" s="2">
+        <v>1.62</v>
+      </c>
+      <c r="O19" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="P19" s="2" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" spans="1:16">
+      <c r="A20" s="2">
+        <v>16</v>
+      </c>
+      <c r="B20" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="C20" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="D20" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="E20" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="F20" s="2">
+        <v>1</v>
+      </c>
+      <c r="G20" s="2">
+        <v>6.0</v>
+      </c>
+      <c r="H20" s="2">
+        <v>10.0</v>
+      </c>
+      <c r="I20" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="J20" s="2">
+        <v>3</v>
+      </c>
+      <c r="K20" s="2">
+        <v>2</v>
+      </c>
+      <c r="L20" s="2"/>
+      <c r="M20" s="2">
+        <v>5</v>
+      </c>
+      <c r="N20" s="2">
+        <v>14.25</v>
+      </c>
+      <c r="O20" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="P20" s="2" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="1:16">
+      <c r="A21" s="2">
+        <v>17</v>
+      </c>
+      <c r="B21" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="C21" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="D21" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="E21" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="F21" s="2">
+        <v>2</v>
+      </c>
+      <c r="G21" s="2">
+        <v>10.0</v>
+      </c>
+      <c r="H21" s="2">
+        <v>10.0</v>
+      </c>
+      <c r="I21" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="J21" s="2">
+        <v>5</v>
+      </c>
+      <c r="K21" s="2"/>
+      <c r="L21" s="2"/>
+      <c r="M21" s="2">
+        <v>5</v>
+      </c>
+      <c r="N21" s="2">
+        <v>3.77</v>
+      </c>
+      <c r="O21" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="P21" s="2" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="1:16">
+      <c r="A22" s="2">
+        <v>18</v>
+      </c>
+      <c r="B22" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="C22" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="D22" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="E22" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="F22" s="2">
+        <v>1</v>
+      </c>
+      <c r="G22" s="2">
+        <v>10.0</v>
+      </c>
+      <c r="H22" s="2">
+        <v>10.0</v>
+      </c>
+      <c r="I22" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="J22" s="2">
+        <v>5</v>
+      </c>
+      <c r="K22" s="2"/>
+      <c r="L22" s="2"/>
+      <c r="M22" s="2">
+        <v>5</v>
+      </c>
+      <c r="N22" s="2">
+        <v>5.62</v>
+      </c>
+      <c r="O22" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="P22" s="2" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="1:16">
+      <c r="A23" s="2">
+        <v>19</v>
+      </c>
+      <c r="B23" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="C23" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="D23" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="E23" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="F23" s="2">
+        <v>1</v>
+      </c>
+      <c r="G23" s="2">
+        <v>8.0</v>
+      </c>
+      <c r="H23" s="2">
+        <v>10.0</v>
+      </c>
+      <c r="I23" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="J23" s="2">
+        <v>4</v>
+      </c>
+      <c r="K23" s="2">
+        <v>1</v>
+      </c>
+      <c r="L23" s="2"/>
+      <c r="M23" s="2">
+        <v>5</v>
+      </c>
+      <c r="N23" s="2">
+        <v>29.93</v>
+      </c>
+      <c r="O23" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="P23" s="2" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" spans="1:16">
+      <c r="A24" s="2">
+        <v>20</v>
+      </c>
+      <c r="B24" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C24" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="D24" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="E24" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="F24" s="2">
+        <v>3</v>
+      </c>
+      <c r="G24" s="2">
+        <v>8.0</v>
+      </c>
+      <c r="H24" s="2">
+        <v>10.0</v>
+      </c>
+      <c r="I24" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="J24" s="2">
+        <v>4</v>
+      </c>
+      <c r="K24" s="2">
+        <v>1</v>
+      </c>
+      <c r="L24" s="2"/>
+      <c r="M24" s="2">
+        <v>5</v>
+      </c>
+      <c r="N24" s="2">
+        <v>69.77</v>
+      </c>
+      <c r="O24" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="P24" s="2" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="1:16">
+      <c r="A25" s="2">
+        <v>21</v>
+      </c>
+      <c r="B25" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="C25" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D25" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E25" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="F25" s="2">
+        <v>1</v>
+      </c>
+      <c r="G25" s="2">
+        <v>10.0</v>
+      </c>
+      <c r="H25" s="2">
+        <v>10.0</v>
+      </c>
+      <c r="I25" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="J25" s="2">
+        <v>5</v>
+      </c>
+      <c r="K25" s="2"/>
+      <c r="L25" s="2"/>
+      <c r="M25" s="2">
+        <v>5</v>
+      </c>
+      <c r="N25" s="2">
+        <v>20.27</v>
+      </c>
+      <c r="O25" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="P25" s="2" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="1:16">
+      <c r="A26" s="2">
+        <v>22</v>
+      </c>
+      <c r="B26" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="C26" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="D26" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="E26" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="F26" s="2">
+        <v>1</v>
+      </c>
+      <c r="G26" s="2">
+        <v>10.0</v>
+      </c>
+      <c r="H26" s="2">
+        <v>10.0</v>
+      </c>
+      <c r="I26" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="J26" s="2">
+        <v>5</v>
+      </c>
+      <c r="K26" s="2"/>
+      <c r="L26" s="2"/>
+      <c r="M26" s="2">
+        <v>5</v>
+      </c>
+      <c r="N26" s="2">
         <v>21.33</v>
       </c>
-      <c r="O13" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="P13" s="2" t="s">
+      <c r="O26" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="P26" s="2" t="s">
         <v>0</v>
       </c>
     </row>

--- a/2lit_online.xlsx
+++ b/2lit_online.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="112">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="128">
   <si>
     <t>ناجح ✓</t>
   </si>
@@ -296,6 +296,54 @@
     <t>Tasneem abdelnasser</t>
   </si>
   <si>
+    <t>2026-03-29 19:43</t>
+  </si>
+  <si>
+    <t>01066525302</t>
+  </si>
+  <si>
+    <t>miroshebl2009@gmail.com</t>
+  </si>
+  <si>
+    <t>omar ahmed mohamed shebl</t>
+  </si>
+  <si>
+    <t>2026-03-29 21:52</t>
+  </si>
+  <si>
+    <t>01002177882</t>
+  </si>
+  <si>
+    <t>rorobaraa2008@gmail.com</t>
+  </si>
+  <si>
+    <t>مريم البراء محمد</t>
+  </si>
+  <si>
+    <t>2026-03-29 23:50</t>
+  </si>
+  <si>
+    <t>01128152846</t>
+  </si>
+  <si>
+    <t>eyad99252@gmail.com</t>
+  </si>
+  <si>
+    <t>اياد محمد حامد</t>
+  </si>
+  <si>
+    <t>2026-03-30 03:14</t>
+  </si>
+  <si>
+    <t>01017101652</t>
+  </si>
+  <si>
+    <t>Eboobaraa@gmail.com</t>
+  </si>
+  <si>
+    <t>إباء البراء محمد</t>
+  </si>
+  <si>
     <t>الحالة</t>
   </si>
   <si>
@@ -350,7 +398,7 @@
     <t>الدرجة الكاملة: 10 | درجة النجاح: 5.00</t>
   </si>
   <si>
-    <t>تاريخ التصدير: 2026-03-29 16:33</t>
+    <t>تاريخ التصدير: 2026-03-30 16:28</t>
   </si>
 </sst>
 </file>
@@ -738,7 +786,7 @@
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
   </sheetPr>
-  <dimension ref="A1:P26"/>
+  <dimension ref="A1:P30"/>
   <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col min="1" max="1" width="6" customWidth="true" style="0"/>
@@ -761,67 +809,67 @@
   <sheetData>
     <row r="1" spans="1:16">
       <c r="A1" s="3" t="s">
-        <v>109</v>
+        <v>125</v>
       </c>
     </row>
     <row r="2" spans="1:16">
       <c r="A2" s="3" t="s">
-        <v>110</v>
+        <v>126</v>
       </c>
     </row>
     <row r="3" spans="1:16">
       <c r="A3" s="3" t="s">
-        <v>111</v>
+        <v>127</v>
       </c>
     </row>
     <row r="4" spans="1:16">
       <c r="A4" s="1" t="s">
-        <v>108</v>
+        <v>124</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>107</v>
+        <v>123</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>106</v>
+        <v>122</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>105</v>
+        <v>121</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>104</v>
+        <v>120</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>103</v>
+        <v>119</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>102</v>
+        <v>118</v>
       </c>
       <c r="H4" s="1" t="s">
-        <v>101</v>
+        <v>117</v>
       </c>
       <c r="I4" s="1" t="s">
-        <v>100</v>
+        <v>116</v>
       </c>
       <c r="J4" s="1" t="s">
-        <v>99</v>
+        <v>115</v>
       </c>
       <c r="K4" s="1" t="s">
-        <v>98</v>
+        <v>114</v>
       </c>
       <c r="L4" s="1" t="s">
-        <v>97</v>
+        <v>113</v>
       </c>
       <c r="M4" s="1" t="s">
-        <v>96</v>
+        <v>112</v>
       </c>
       <c r="N4" s="1" t="s">
-        <v>95</v>
+        <v>111</v>
       </c>
       <c r="O4" s="1" t="s">
-        <v>94</v>
+        <v>110</v>
       </c>
       <c r="P4" s="1" t="s">
-        <v>93</v>
+        <v>109</v>
       </c>
     </row>
     <row r="5" spans="1:16">
@@ -829,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>92</v>
+        <v>108</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>91</v>
+        <v>107</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>90</v>
+        <v>106</v>
       </c>
       <c r="E5" s="2" t="s">
         <v>3</v>
@@ -844,27 +892,29 @@
         <v>1</v>
       </c>
       <c r="G5" s="2">
-        <v>10.0</v>
+        <v>6.0</v>
       </c>
       <c r="H5" s="2">
         <v>10.0</v>
       </c>
       <c r="I5" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="J5" s="2">
+        <v>3</v>
+      </c>
+      <c r="K5" s="2">
         <v>2</v>
       </c>
-      <c r="J5" s="2">
-        <v>5</v>
-      </c>
-      <c r="K5" s="2"/>
       <c r="L5" s="2"/>
       <c r="M5" s="2">
         <v>5</v>
       </c>
       <c r="N5" s="2">
-        <v>20.67</v>
+        <v>27.28</v>
       </c>
       <c r="O5" s="2" t="s">
-        <v>89</v>
+        <v>105</v>
       </c>
       <c r="P5" s="2" t="s">
         <v>0</v>
@@ -875,42 +925,44 @@
         <v>2</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>88</v>
+        <v>104</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>87</v>
+        <v>103</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>86</v>
+        <v>102</v>
       </c>
       <c r="E6" s="2" t="s">
         <v>3</v>
       </c>
       <c r="F6" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G6" s="2">
-        <v>10.0</v>
+        <v>8.0</v>
       </c>
       <c r="H6" s="2">
         <v>10.0</v>
       </c>
       <c r="I6" s="2" t="s">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="J6" s="2">
-        <v>5</v>
-      </c>
-      <c r="K6" s="2"/>
+        <v>4</v>
+      </c>
+      <c r="K6" s="2">
+        <v>1</v>
+      </c>
       <c r="L6" s="2"/>
       <c r="M6" s="2">
         <v>5</v>
       </c>
       <c r="N6" s="2">
-        <v>10.48</v>
+        <v>13.37</v>
       </c>
       <c r="O6" s="2" t="s">
-        <v>85</v>
+        <v>101</v>
       </c>
       <c r="P6" s="2" t="s">
         <v>0</v>
@@ -921,13 +973,13 @@
         <v>3</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>84</v>
+        <v>100</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>83</v>
+        <v>99</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>82</v>
+        <v>98</v>
       </c>
       <c r="E7" s="2" t="s">
         <v>3</v>
@@ -953,10 +1005,10 @@
         <v>5</v>
       </c>
       <c r="N7" s="2">
-        <v>2.65</v>
+        <v>23.13</v>
       </c>
       <c r="O7" s="2" t="s">
-        <v>81</v>
+        <v>97</v>
       </c>
       <c r="P7" s="2" t="s">
         <v>0</v>
@@ -967,13 +1019,13 @@
         <v>4</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>80</v>
+        <v>96</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>79</v>
+        <v>95</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>78</v>
+        <v>94</v>
       </c>
       <c r="E8" s="2" t="s">
         <v>3</v>
@@ -982,27 +1034,29 @@
         <v>1</v>
       </c>
       <c r="G8" s="2">
-        <v>10.0</v>
+        <v>8.0</v>
       </c>
       <c r="H8" s="2">
         <v>10.0</v>
       </c>
       <c r="I8" s="2" t="s">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="J8" s="2">
-        <v>5</v>
-      </c>
-      <c r="K8" s="2"/>
+        <v>4</v>
+      </c>
+      <c r="K8" s="2">
+        <v>1</v>
+      </c>
       <c r="L8" s="2"/>
       <c r="M8" s="2">
         <v>5</v>
       </c>
       <c r="N8" s="2">
-        <v>11.3</v>
+        <v>11.15</v>
       </c>
       <c r="O8" s="2" t="s">
-        <v>77</v>
+        <v>93</v>
       </c>
       <c r="P8" s="2" t="s">
         <v>0</v>
@@ -1013,13 +1067,13 @@
         <v>5</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>76</v>
+        <v>92</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>75</v>
+        <v>91</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>74</v>
+        <v>90</v>
       </c>
       <c r="E9" s="2" t="s">
         <v>3</v>
@@ -1045,10 +1099,10 @@
         <v>5</v>
       </c>
       <c r="N9" s="2">
-        <v>11.27</v>
+        <v>20.67</v>
       </c>
       <c r="O9" s="2" t="s">
-        <v>73</v>
+        <v>89</v>
       </c>
       <c r="P9" s="2" t="s">
         <v>0</v>
@@ -1059,13 +1113,13 @@
         <v>6</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>72</v>
+        <v>88</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>71</v>
+        <v>87</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>70</v>
+        <v>86</v>
       </c>
       <c r="E10" s="2" t="s">
         <v>3</v>
@@ -1074,29 +1128,27 @@
         <v>1</v>
       </c>
       <c r="G10" s="2">
-        <v>8.0</v>
+        <v>10.0</v>
       </c>
       <c r="H10" s="2">
         <v>10.0</v>
       </c>
       <c r="I10" s="2" t="s">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="J10" s="2">
-        <v>4</v>
-      </c>
-      <c r="K10" s="2">
-        <v>1</v>
-      </c>
+        <v>5</v>
+      </c>
+      <c r="K10" s="2"/>
       <c r="L10" s="2"/>
       <c r="M10" s="2">
         <v>5</v>
       </c>
       <c r="N10" s="2">
-        <v>7.5</v>
+        <v>10.48</v>
       </c>
       <c r="O10" s="2" t="s">
-        <v>69</v>
+        <v>85</v>
       </c>
       <c r="P10" s="2" t="s">
         <v>0</v>
@@ -1107,13 +1159,13 @@
         <v>7</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>68</v>
+        <v>84</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>67</v>
+        <v>83</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>66</v>
+        <v>82</v>
       </c>
       <c r="E11" s="2" t="s">
         <v>3</v>
@@ -1139,10 +1191,10 @@
         <v>5</v>
       </c>
       <c r="N11" s="2">
-        <v>5.17</v>
+        <v>2.65</v>
       </c>
       <c r="O11" s="2" t="s">
-        <v>65</v>
+        <v>81</v>
       </c>
       <c r="P11" s="2" t="s">
         <v>0</v>
@@ -1153,13 +1205,13 @@
         <v>8</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>64</v>
+        <v>80</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>63</v>
+        <v>79</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>62</v>
+        <v>78</v>
       </c>
       <c r="E12" s="2" t="s">
         <v>3</v>
@@ -1168,29 +1220,27 @@
         <v>1</v>
       </c>
       <c r="G12" s="2">
-        <v>8.0</v>
+        <v>10.0</v>
       </c>
       <c r="H12" s="2">
         <v>10.0</v>
       </c>
       <c r="I12" s="2" t="s">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="J12" s="2">
-        <v>4</v>
-      </c>
-      <c r="K12" s="2">
-        <v>1</v>
-      </c>
+        <v>5</v>
+      </c>
+      <c r="K12" s="2"/>
       <c r="L12" s="2"/>
       <c r="M12" s="2">
         <v>5</v>
       </c>
       <c r="N12" s="2">
-        <v>10.48</v>
+        <v>11.3</v>
       </c>
       <c r="O12" s="2" t="s">
-        <v>61</v>
+        <v>77</v>
       </c>
       <c r="P12" s="2" t="s">
         <v>0</v>
@@ -1201,13 +1251,13 @@
         <v>9</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>60</v>
+        <v>76</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>59</v>
+        <v>75</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>58</v>
+        <v>74</v>
       </c>
       <c r="E13" s="2" t="s">
         <v>3</v>
@@ -1216,29 +1266,27 @@
         <v>1</v>
       </c>
       <c r="G13" s="2">
-        <v>8.0</v>
+        <v>10.0</v>
       </c>
       <c r="H13" s="2">
         <v>10.0</v>
       </c>
       <c r="I13" s="2" t="s">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="J13" s="2">
-        <v>4</v>
-      </c>
-      <c r="K13" s="2">
-        <v>1</v>
-      </c>
+        <v>5</v>
+      </c>
+      <c r="K13" s="2"/>
       <c r="L13" s="2"/>
       <c r="M13" s="2">
         <v>5</v>
       </c>
       <c r="N13" s="2">
-        <v>29.6</v>
+        <v>11.27</v>
       </c>
       <c r="O13" s="2" t="s">
-        <v>57</v>
+        <v>73</v>
       </c>
       <c r="P13" s="2" t="s">
         <v>0</v>
@@ -1249,13 +1297,13 @@
         <v>10</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>56</v>
+        <v>72</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>55</v>
+        <v>71</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>54</v>
+        <v>70</v>
       </c>
       <c r="E14" s="2" t="s">
         <v>3</v>
@@ -1264,27 +1312,29 @@
         <v>1</v>
       </c>
       <c r="G14" s="2">
-        <v>10.0</v>
+        <v>8.0</v>
       </c>
       <c r="H14" s="2">
         <v>10.0</v>
       </c>
       <c r="I14" s="2" t="s">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="J14" s="2">
-        <v>5</v>
-      </c>
-      <c r="K14" s="2"/>
+        <v>4</v>
+      </c>
+      <c r="K14" s="2">
+        <v>1</v>
+      </c>
       <c r="L14" s="2"/>
       <c r="M14" s="2">
         <v>5</v>
       </c>
       <c r="N14" s="2">
-        <v>4.43</v>
+        <v>7.5</v>
       </c>
       <c r="O14" s="2" t="s">
-        <v>53</v>
+        <v>69</v>
       </c>
       <c r="P14" s="2" t="s">
         <v>0</v>
@@ -1295,13 +1345,13 @@
         <v>11</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>52</v>
+        <v>68</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>51</v>
+        <v>67</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>50</v>
+        <v>66</v>
       </c>
       <c r="E15" s="2" t="s">
         <v>3</v>
@@ -1327,10 +1377,10 @@
         <v>5</v>
       </c>
       <c r="N15" s="2">
-        <v>7.9</v>
+        <v>5.17</v>
       </c>
       <c r="O15" s="2" t="s">
-        <v>49</v>
+        <v>65</v>
       </c>
       <c r="P15" s="2" t="s">
         <v>0</v>
@@ -1341,13 +1391,13 @@
         <v>12</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>48</v>
+        <v>64</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>47</v>
+        <v>63</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>46</v>
+        <v>62</v>
       </c>
       <c r="E16" s="2" t="s">
         <v>3</v>
@@ -1356,27 +1406,29 @@
         <v>1</v>
       </c>
       <c r="G16" s="2">
-        <v>10.0</v>
+        <v>8.0</v>
       </c>
       <c r="H16" s="2">
         <v>10.0</v>
       </c>
       <c r="I16" s="2" t="s">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="J16" s="2">
-        <v>5</v>
-      </c>
-      <c r="K16" s="2"/>
+        <v>4</v>
+      </c>
+      <c r="K16" s="2">
+        <v>1</v>
+      </c>
       <c r="L16" s="2"/>
       <c r="M16" s="2">
         <v>5</v>
       </c>
       <c r="N16" s="2">
-        <v>12.17</v>
+        <v>10.48</v>
       </c>
       <c r="O16" s="2" t="s">
-        <v>45</v>
+        <v>61</v>
       </c>
       <c r="P16" s="2" t="s">
         <v>0</v>
@@ -1387,13 +1439,13 @@
         <v>13</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>44</v>
+        <v>60</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>43</v>
+        <v>59</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>42</v>
+        <v>58</v>
       </c>
       <c r="E17" s="2" t="s">
         <v>3</v>
@@ -1402,27 +1454,29 @@
         <v>1</v>
       </c>
       <c r="G17" s="2">
-        <v>10.0</v>
+        <v>8.0</v>
       </c>
       <c r="H17" s="2">
         <v>10.0</v>
       </c>
       <c r="I17" s="2" t="s">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="J17" s="2">
-        <v>5</v>
-      </c>
-      <c r="K17" s="2"/>
+        <v>4</v>
+      </c>
+      <c r="K17" s="2">
+        <v>1</v>
+      </c>
       <c r="L17" s="2"/>
       <c r="M17" s="2">
         <v>5</v>
       </c>
       <c r="N17" s="2">
-        <v>2.65</v>
+        <v>29.6</v>
       </c>
       <c r="O17" s="2" t="s">
-        <v>41</v>
+        <v>57</v>
       </c>
       <c r="P17" s="2" t="s">
         <v>0</v>
@@ -1433,13 +1487,13 @@
         <v>14</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>40</v>
+        <v>56</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>39</v>
+        <v>55</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>38</v>
+        <v>54</v>
       </c>
       <c r="E18" s="2" t="s">
         <v>3</v>
@@ -1448,29 +1502,27 @@
         <v>1</v>
       </c>
       <c r="G18" s="2">
-        <v>8.0</v>
+        <v>10.0</v>
       </c>
       <c r="H18" s="2">
         <v>10.0</v>
       </c>
       <c r="I18" s="2" t="s">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="J18" s="2">
-        <v>4</v>
-      </c>
-      <c r="K18" s="2">
-        <v>1</v>
-      </c>
+        <v>5</v>
+      </c>
+      <c r="K18" s="2"/>
       <c r="L18" s="2"/>
       <c r="M18" s="2">
         <v>5</v>
       </c>
       <c r="N18" s="2">
-        <v>14.27</v>
+        <v>4.43</v>
       </c>
       <c r="O18" s="2" t="s">
-        <v>37</v>
+        <v>53</v>
       </c>
       <c r="P18" s="2" t="s">
         <v>0</v>
@@ -1481,44 +1533,42 @@
         <v>15</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>36</v>
+        <v>52</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>35</v>
+        <v>51</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>34</v>
+        <v>50</v>
       </c>
       <c r="E19" s="2" t="s">
         <v>3</v>
       </c>
       <c r="F19" s="2">
+        <v>1</v>
+      </c>
+      <c r="G19" s="2">
+        <v>10.0</v>
+      </c>
+      <c r="H19" s="2">
+        <v>10.0</v>
+      </c>
+      <c r="I19" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="G19" s="2">
-        <v>6.0</v>
-      </c>
-      <c r="H19" s="2">
-        <v>10.0</v>
-      </c>
-      <c r="I19" s="2" t="s">
-        <v>29</v>
-      </c>
       <c r="J19" s="2">
-        <v>3</v>
-      </c>
-      <c r="K19" s="2">
-        <v>2</v>
-      </c>
+        <v>5</v>
+      </c>
+      <c r="K19" s="2"/>
       <c r="L19" s="2"/>
       <c r="M19" s="2">
         <v>5</v>
       </c>
       <c r="N19" s="2">
-        <v>1.62</v>
+        <v>7.9</v>
       </c>
       <c r="O19" s="2" t="s">
-        <v>33</v>
+        <v>49</v>
       </c>
       <c r="P19" s="2" t="s">
         <v>0</v>
@@ -1529,13 +1579,13 @@
         <v>16</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>32</v>
+        <v>48</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>31</v>
+        <v>47</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>30</v>
+        <v>46</v>
       </c>
       <c r="E20" s="2" t="s">
         <v>3</v>
@@ -1544,29 +1594,27 @@
         <v>1</v>
       </c>
       <c r="G20" s="2">
-        <v>6.0</v>
+        <v>10.0</v>
       </c>
       <c r="H20" s="2">
         <v>10.0</v>
       </c>
       <c r="I20" s="2" t="s">
-        <v>29</v>
+        <v>2</v>
       </c>
       <c r="J20" s="2">
-        <v>3</v>
-      </c>
-      <c r="K20" s="2">
-        <v>2</v>
-      </c>
+        <v>5</v>
+      </c>
+      <c r="K20" s="2"/>
       <c r="L20" s="2"/>
       <c r="M20" s="2">
         <v>5</v>
       </c>
       <c r="N20" s="2">
-        <v>14.25</v>
+        <v>12.17</v>
       </c>
       <c r="O20" s="2" t="s">
-        <v>28</v>
+        <v>45</v>
       </c>
       <c r="P20" s="2" t="s">
         <v>0</v>
@@ -1577,19 +1625,19 @@
         <v>17</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>27</v>
+        <v>44</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>26</v>
+        <v>43</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>25</v>
+        <v>42</v>
       </c>
       <c r="E21" s="2" t="s">
         <v>3</v>
       </c>
       <c r="F21" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G21" s="2">
         <v>10.0</v>
@@ -1609,10 +1657,10 @@
         <v>5</v>
       </c>
       <c r="N21" s="2">
-        <v>3.77</v>
+        <v>2.65</v>
       </c>
       <c r="O21" s="2" t="s">
-        <v>24</v>
+        <v>41</v>
       </c>
       <c r="P21" s="2" t="s">
         <v>0</v>
@@ -1623,13 +1671,13 @@
         <v>18</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>23</v>
+        <v>40</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>22</v>
+        <v>39</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>21</v>
+        <v>38</v>
       </c>
       <c r="E22" s="2" t="s">
         <v>3</v>
@@ -1638,27 +1686,29 @@
         <v>1</v>
       </c>
       <c r="G22" s="2">
-        <v>10.0</v>
+        <v>8.0</v>
       </c>
       <c r="H22" s="2">
         <v>10.0</v>
       </c>
       <c r="I22" s="2" t="s">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="J22" s="2">
-        <v>5</v>
-      </c>
-      <c r="K22" s="2"/>
+        <v>4</v>
+      </c>
+      <c r="K22" s="2">
+        <v>1</v>
+      </c>
       <c r="L22" s="2"/>
       <c r="M22" s="2">
         <v>5</v>
       </c>
       <c r="N22" s="2">
-        <v>5.62</v>
+        <v>14.27</v>
       </c>
       <c r="O22" s="2" t="s">
-        <v>20</v>
+        <v>37</v>
       </c>
       <c r="P22" s="2" t="s">
         <v>0</v>
@@ -1669,44 +1719,44 @@
         <v>19</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>19</v>
+        <v>36</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>18</v>
+        <v>35</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>17</v>
+        <v>34</v>
       </c>
       <c r="E23" s="2" t="s">
         <v>3</v>
       </c>
       <c r="F23" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G23" s="2">
-        <v>8.0</v>
+        <v>6.0</v>
       </c>
       <c r="H23" s="2">
         <v>10.0</v>
       </c>
       <c r="I23" s="2" t="s">
-        <v>12</v>
+        <v>29</v>
       </c>
       <c r="J23" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K23" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L23" s="2"/>
       <c r="M23" s="2">
         <v>5</v>
       </c>
       <c r="N23" s="2">
-        <v>29.93</v>
+        <v>1.62</v>
       </c>
       <c r="O23" s="2" t="s">
-        <v>16</v>
+        <v>33</v>
       </c>
       <c r="P23" s="2" t="s">
         <v>0</v>
@@ -1717,44 +1767,44 @@
         <v>20</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>15</v>
+        <v>32</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>14</v>
+        <v>31</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>13</v>
+        <v>30</v>
       </c>
       <c r="E24" s="2" t="s">
         <v>3</v>
       </c>
       <c r="F24" s="2">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G24" s="2">
-        <v>8.0</v>
+        <v>6.0</v>
       </c>
       <c r="H24" s="2">
         <v>10.0</v>
       </c>
       <c r="I24" s="2" t="s">
-        <v>12</v>
+        <v>29</v>
       </c>
       <c r="J24" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K24" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L24" s="2"/>
       <c r="M24" s="2">
         <v>5</v>
       </c>
       <c r="N24" s="2">
-        <v>69.77</v>
+        <v>14.25</v>
       </c>
       <c r="O24" s="2" t="s">
-        <v>11</v>
+        <v>28</v>
       </c>
       <c r="P24" s="2" t="s">
         <v>0</v>
@@ -1765,19 +1815,19 @@
         <v>21</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>10</v>
+        <v>27</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>9</v>
+        <v>26</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>8</v>
+        <v>25</v>
       </c>
       <c r="E25" s="2" t="s">
         <v>3</v>
       </c>
       <c r="F25" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G25" s="2">
         <v>10.0</v>
@@ -1797,10 +1847,10 @@
         <v>5</v>
       </c>
       <c r="N25" s="2">
-        <v>20.27</v>
+        <v>3.77</v>
       </c>
       <c r="O25" s="2" t="s">
-        <v>7</v>
+        <v>24</v>
       </c>
       <c r="P25" s="2" t="s">
         <v>0</v>
@@ -1811,13 +1861,13 @@
         <v>22</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>6</v>
+        <v>23</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>5</v>
+        <v>22</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>4</v>
+        <v>21</v>
       </c>
       <c r="E26" s="2" t="s">
         <v>3</v>
@@ -1843,12 +1893,200 @@
         <v>5</v>
       </c>
       <c r="N26" s="2">
+        <v>5.62</v>
+      </c>
+      <c r="O26" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="P26" s="2" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" spans="1:16">
+      <c r="A27" s="2">
+        <v>23</v>
+      </c>
+      <c r="B27" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="C27" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="D27" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="E27" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="F27" s="2">
+        <v>1</v>
+      </c>
+      <c r="G27" s="2">
+        <v>8.0</v>
+      </c>
+      <c r="H27" s="2">
+        <v>10.0</v>
+      </c>
+      <c r="I27" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="J27" s="2">
+        <v>4</v>
+      </c>
+      <c r="K27" s="2">
+        <v>1</v>
+      </c>
+      <c r="L27" s="2"/>
+      <c r="M27" s="2">
+        <v>5</v>
+      </c>
+      <c r="N27" s="2">
+        <v>29.93</v>
+      </c>
+      <c r="O27" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="P27" s="2" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28" spans="1:16">
+      <c r="A28" s="2">
+        <v>24</v>
+      </c>
+      <c r="B28" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C28" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="D28" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="E28" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="F28" s="2">
+        <v>3</v>
+      </c>
+      <c r="G28" s="2">
+        <v>8.0</v>
+      </c>
+      <c r="H28" s="2">
+        <v>10.0</v>
+      </c>
+      <c r="I28" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="J28" s="2">
+        <v>4</v>
+      </c>
+      <c r="K28" s="2">
+        <v>1</v>
+      </c>
+      <c r="L28" s="2"/>
+      <c r="M28" s="2">
+        <v>5</v>
+      </c>
+      <c r="N28" s="2">
+        <v>69.77</v>
+      </c>
+      <c r="O28" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="P28" s="2" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="1:16">
+      <c r="A29" s="2">
+        <v>25</v>
+      </c>
+      <c r="B29" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="C29" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D29" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E29" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="F29" s="2">
+        <v>1</v>
+      </c>
+      <c r="G29" s="2">
+        <v>10.0</v>
+      </c>
+      <c r="H29" s="2">
+        <v>10.0</v>
+      </c>
+      <c r="I29" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="J29" s="2">
+        <v>5</v>
+      </c>
+      <c r="K29" s="2"/>
+      <c r="L29" s="2"/>
+      <c r="M29" s="2">
+        <v>5</v>
+      </c>
+      <c r="N29" s="2">
+        <v>20.27</v>
+      </c>
+      <c r="O29" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="P29" s="2" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="1:16">
+      <c r="A30" s="2">
+        <v>26</v>
+      </c>
+      <c r="B30" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="C30" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="D30" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="E30" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="F30" s="2">
+        <v>1</v>
+      </c>
+      <c r="G30" s="2">
+        <v>10.0</v>
+      </c>
+      <c r="H30" s="2">
+        <v>10.0</v>
+      </c>
+      <c r="I30" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="J30" s="2">
+        <v>5</v>
+      </c>
+      <c r="K30" s="2"/>
+      <c r="L30" s="2"/>
+      <c r="M30" s="2">
+        <v>5</v>
+      </c>
+      <c r="N30" s="2">
         <v>21.33</v>
       </c>
-      <c r="O26" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="P26" s="2" t="s">
+      <c r="O30" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="P30" s="2" t="s">
         <v>0</v>
       </c>
     </row>

--- a/2lit_online.xlsx
+++ b/2lit_online.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="128">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="138">
   <si>
     <t>ناجح ✓</t>
   </si>
@@ -344,6 +344,36 @@
     <t>إباء البراء محمد</t>
   </si>
   <si>
+    <t>2026-04-01 16:41</t>
+  </si>
+  <si>
+    <t>01008903957</t>
+  </si>
+  <si>
+    <t>Nofa_85@hotmail</t>
+  </si>
+  <si>
+    <t>موسي محمد  مؤنس</t>
+  </si>
+  <si>
+    <t>راسب ✗</t>
+  </si>
+  <si>
+    <t>2026-04-05 15:22</t>
+  </si>
+  <si>
+    <t>40.0%</t>
+  </si>
+  <si>
+    <t>01016073802</t>
+  </si>
+  <si>
+    <t>medo.baraa2008@gmail.com</t>
+  </si>
+  <si>
+    <t>Mohamed albaraa mohamed mansour</t>
+  </si>
+  <si>
     <t>الحالة</t>
   </si>
   <si>
@@ -398,7 +428,7 @@
     <t>الدرجة الكاملة: 10 | درجة النجاح: 5.00</t>
   </si>
   <si>
-    <t>تاريخ التصدير: 2026-03-30 16:28</t>
+    <t>تاريخ التصدير: 2026-04-05 16:57</t>
   </si>
 </sst>
 </file>
@@ -786,7 +816,7 @@
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
   </sheetPr>
-  <dimension ref="A1:P30"/>
+  <dimension ref="A1:P32"/>
   <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col min="1" max="1" width="6" customWidth="true" style="0"/>
@@ -809,67 +839,67 @@
   <sheetData>
     <row r="1" spans="1:16">
       <c r="A1" s="3" t="s">
-        <v>125</v>
+        <v>135</v>
       </c>
     </row>
     <row r="2" spans="1:16">
       <c r="A2" s="3" t="s">
-        <v>126</v>
+        <v>136</v>
       </c>
     </row>
     <row r="3" spans="1:16">
       <c r="A3" s="3" t="s">
-        <v>127</v>
+        <v>137</v>
       </c>
     </row>
     <row r="4" spans="1:16">
       <c r="A4" s="1" t="s">
+        <v>134</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>133</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>131</v>
+      </c>
+      <c r="E4" s="1" t="s">
+        <v>130</v>
+      </c>
+      <c r="F4" s="1" t="s">
+        <v>129</v>
+      </c>
+      <c r="G4" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="H4" s="1" t="s">
+        <v>127</v>
+      </c>
+      <c r="I4" s="1" t="s">
+        <v>126</v>
+      </c>
+      <c r="J4" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="K4" s="1" t="s">
         <v>124</v>
       </c>
-      <c r="B4" s="1" t="s">
+      <c r="L4" s="1" t="s">
         <v>123</v>
       </c>
-      <c r="C4" s="1" t="s">
+      <c r="M4" s="1" t="s">
         <v>122</v>
       </c>
-      <c r="D4" s="1" t="s">
+      <c r="N4" s="1" t="s">
         <v>121</v>
       </c>
-      <c r="E4" s="1" t="s">
+      <c r="O4" s="1" t="s">
         <v>120</v>
       </c>
-      <c r="F4" s="1" t="s">
+      <c r="P4" s="1" t="s">
         <v>119</v>
-      </c>
-      <c r="G4" s="1" t="s">
-        <v>118</v>
-      </c>
-      <c r="H4" s="1" t="s">
-        <v>117</v>
-      </c>
-      <c r="I4" s="1" t="s">
-        <v>116</v>
-      </c>
-      <c r="J4" s="1" t="s">
-        <v>115</v>
-      </c>
-      <c r="K4" s="1" t="s">
-        <v>114</v>
-      </c>
-      <c r="L4" s="1" t="s">
-        <v>113</v>
-      </c>
-      <c r="M4" s="1" t="s">
-        <v>112</v>
-      </c>
-      <c r="N4" s="1" t="s">
-        <v>111</v>
-      </c>
-      <c r="O4" s="1" t="s">
-        <v>110</v>
-      </c>
-      <c r="P4" s="1" t="s">
-        <v>109</v>
       </c>
     </row>
     <row r="5" spans="1:16">
@@ -877,47 +907,47 @@
         <v>1</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>108</v>
+        <v>118</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>107</v>
+        <v>117</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>106</v>
+        <v>116</v>
       </c>
       <c r="E5" s="2" t="s">
         <v>3</v>
       </c>
       <c r="F5" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G5" s="2">
-        <v>6.0</v>
+        <v>4.0</v>
       </c>
       <c r="H5" s="2">
         <v>10.0</v>
       </c>
       <c r="I5" s="2" t="s">
-        <v>29</v>
+        <v>115</v>
       </c>
       <c r="J5" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K5" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L5" s="2"/>
       <c r="M5" s="2">
         <v>5</v>
       </c>
       <c r="N5" s="2">
-        <v>27.28</v>
+        <v>1.73</v>
       </c>
       <c r="O5" s="2" t="s">
-        <v>105</v>
+        <v>114</v>
       </c>
       <c r="P5" s="2" t="s">
-        <v>0</v>
+        <v>113</v>
       </c>
     </row>
     <row r="6" spans="1:16">
@@ -925,19 +955,19 @@
         <v>2</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>104</v>
+        <v>112</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>103</v>
+        <v>111</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>102</v>
+        <v>110</v>
       </c>
       <c r="E6" s="2" t="s">
         <v>3</v>
       </c>
       <c r="F6" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G6" s="2">
         <v>8.0</v>
@@ -959,10 +989,10 @@
         <v>5</v>
       </c>
       <c r="N6" s="2">
-        <v>13.37</v>
+        <v>9.75</v>
       </c>
       <c r="O6" s="2" t="s">
-        <v>101</v>
+        <v>109</v>
       </c>
       <c r="P6" s="2" t="s">
         <v>0</v>
@@ -973,13 +1003,13 @@
         <v>3</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>100</v>
+        <v>108</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>99</v>
+        <v>107</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>98</v>
+        <v>106</v>
       </c>
       <c r="E7" s="2" t="s">
         <v>3</v>
@@ -988,27 +1018,29 @@
         <v>1</v>
       </c>
       <c r="G7" s="2">
-        <v>10.0</v>
+        <v>6.0</v>
       </c>
       <c r="H7" s="2">
         <v>10.0</v>
       </c>
       <c r="I7" s="2" t="s">
-        <v>2</v>
+        <v>29</v>
       </c>
       <c r="J7" s="2">
-        <v>5</v>
-      </c>
-      <c r="K7" s="2"/>
+        <v>3</v>
+      </c>
+      <c r="K7" s="2">
+        <v>2</v>
+      </c>
       <c r="L7" s="2"/>
       <c r="M7" s="2">
         <v>5</v>
       </c>
       <c r="N7" s="2">
-        <v>23.13</v>
+        <v>27.28</v>
       </c>
       <c r="O7" s="2" t="s">
-        <v>97</v>
+        <v>105</v>
       </c>
       <c r="P7" s="2" t="s">
         <v>0</v>
@@ -1019,19 +1051,19 @@
         <v>4</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>96</v>
+        <v>104</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>95</v>
+        <v>103</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>94</v>
+        <v>102</v>
       </c>
       <c r="E8" s="2" t="s">
         <v>3</v>
       </c>
       <c r="F8" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G8" s="2">
         <v>8.0</v>
@@ -1053,10 +1085,10 @@
         <v>5</v>
       </c>
       <c r="N8" s="2">
-        <v>11.15</v>
+        <v>13.37</v>
       </c>
       <c r="O8" s="2" t="s">
-        <v>93</v>
+        <v>101</v>
       </c>
       <c r="P8" s="2" t="s">
         <v>0</v>
@@ -1067,13 +1099,13 @@
         <v>5</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>92</v>
+        <v>100</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>91</v>
+        <v>99</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>90</v>
+        <v>98</v>
       </c>
       <c r="E9" s="2" t="s">
         <v>3</v>
@@ -1099,10 +1131,10 @@
         <v>5</v>
       </c>
       <c r="N9" s="2">
-        <v>20.67</v>
+        <v>23.13</v>
       </c>
       <c r="O9" s="2" t="s">
-        <v>89</v>
+        <v>97</v>
       </c>
       <c r="P9" s="2" t="s">
         <v>0</v>
@@ -1113,13 +1145,13 @@
         <v>6</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>88</v>
+        <v>96</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>87</v>
+        <v>95</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>86</v>
+        <v>94</v>
       </c>
       <c r="E10" s="2" t="s">
         <v>3</v>
@@ -1128,27 +1160,29 @@
         <v>1</v>
       </c>
       <c r="G10" s="2">
-        <v>10.0</v>
+        <v>8.0</v>
       </c>
       <c r="H10" s="2">
         <v>10.0</v>
       </c>
       <c r="I10" s="2" t="s">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="J10" s="2">
-        <v>5</v>
-      </c>
-      <c r="K10" s="2"/>
+        <v>4</v>
+      </c>
+      <c r="K10" s="2">
+        <v>1</v>
+      </c>
       <c r="L10" s="2"/>
       <c r="M10" s="2">
         <v>5</v>
       </c>
       <c r="N10" s="2">
-        <v>10.48</v>
+        <v>11.15</v>
       </c>
       <c r="O10" s="2" t="s">
-        <v>85</v>
+        <v>93</v>
       </c>
       <c r="P10" s="2" t="s">
         <v>0</v>
@@ -1159,13 +1193,13 @@
         <v>7</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>84</v>
+        <v>92</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>83</v>
+        <v>91</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>82</v>
+        <v>90</v>
       </c>
       <c r="E11" s="2" t="s">
         <v>3</v>
@@ -1191,10 +1225,10 @@
         <v>5</v>
       </c>
       <c r="N11" s="2">
-        <v>2.65</v>
+        <v>20.67</v>
       </c>
       <c r="O11" s="2" t="s">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="P11" s="2" t="s">
         <v>0</v>
@@ -1205,13 +1239,13 @@
         <v>8</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="E12" s="2" t="s">
         <v>3</v>
@@ -1237,10 +1271,10 @@
         <v>5</v>
       </c>
       <c r="N12" s="2">
-        <v>11.3</v>
+        <v>10.48</v>
       </c>
       <c r="O12" s="2" t="s">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="P12" s="2" t="s">
         <v>0</v>
@@ -1251,13 +1285,13 @@
         <v>9</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>76</v>
+        <v>84</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>75</v>
+        <v>83</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>74</v>
+        <v>82</v>
       </c>
       <c r="E13" s="2" t="s">
         <v>3</v>
@@ -1283,10 +1317,10 @@
         <v>5</v>
       </c>
       <c r="N13" s="2">
-        <v>11.27</v>
+        <v>2.65</v>
       </c>
       <c r="O13" s="2" t="s">
-        <v>73</v>
+        <v>81</v>
       </c>
       <c r="P13" s="2" t="s">
         <v>0</v>
@@ -1297,13 +1331,13 @@
         <v>10</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>72</v>
+        <v>80</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>71</v>
+        <v>79</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>70</v>
+        <v>78</v>
       </c>
       <c r="E14" s="2" t="s">
         <v>3</v>
@@ -1312,29 +1346,27 @@
         <v>1</v>
       </c>
       <c r="G14" s="2">
-        <v>8.0</v>
+        <v>10.0</v>
       </c>
       <c r="H14" s="2">
         <v>10.0</v>
       </c>
       <c r="I14" s="2" t="s">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="J14" s="2">
-        <v>4</v>
-      </c>
-      <c r="K14" s="2">
-        <v>1</v>
-      </c>
+        <v>5</v>
+      </c>
+      <c r="K14" s="2"/>
       <c r="L14" s="2"/>
       <c r="M14" s="2">
         <v>5</v>
       </c>
       <c r="N14" s="2">
-        <v>7.5</v>
+        <v>11.3</v>
       </c>
       <c r="O14" s="2" t="s">
-        <v>69</v>
+        <v>77</v>
       </c>
       <c r="P14" s="2" t="s">
         <v>0</v>
@@ -1345,13 +1377,13 @@
         <v>11</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>68</v>
+        <v>76</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>67</v>
+        <v>75</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>66</v>
+        <v>74</v>
       </c>
       <c r="E15" s="2" t="s">
         <v>3</v>
@@ -1377,10 +1409,10 @@
         <v>5</v>
       </c>
       <c r="N15" s="2">
-        <v>5.17</v>
+        <v>11.27</v>
       </c>
       <c r="O15" s="2" t="s">
-        <v>65</v>
+        <v>73</v>
       </c>
       <c r="P15" s="2" t="s">
         <v>0</v>
@@ -1391,13 +1423,13 @@
         <v>12</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>64</v>
+        <v>72</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>63</v>
+        <v>71</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>62</v>
+        <v>70</v>
       </c>
       <c r="E16" s="2" t="s">
         <v>3</v>
@@ -1425,10 +1457,10 @@
         <v>5</v>
       </c>
       <c r="N16" s="2">
-        <v>10.48</v>
+        <v>7.5</v>
       </c>
       <c r="O16" s="2" t="s">
-        <v>61</v>
+        <v>69</v>
       </c>
       <c r="P16" s="2" t="s">
         <v>0</v>
@@ -1439,13 +1471,13 @@
         <v>13</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>60</v>
+        <v>68</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>59</v>
+        <v>67</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>58</v>
+        <v>66</v>
       </c>
       <c r="E17" s="2" t="s">
         <v>3</v>
@@ -1454,29 +1486,27 @@
         <v>1</v>
       </c>
       <c r="G17" s="2">
-        <v>8.0</v>
+        <v>10.0</v>
       </c>
       <c r="H17" s="2">
         <v>10.0</v>
       </c>
       <c r="I17" s="2" t="s">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="J17" s="2">
-        <v>4</v>
-      </c>
-      <c r="K17" s="2">
-        <v>1</v>
-      </c>
+        <v>5</v>
+      </c>
+      <c r="K17" s="2"/>
       <c r="L17" s="2"/>
       <c r="M17" s="2">
         <v>5</v>
       </c>
       <c r="N17" s="2">
-        <v>29.6</v>
+        <v>5.17</v>
       </c>
       <c r="O17" s="2" t="s">
-        <v>57</v>
+        <v>65</v>
       </c>
       <c r="P17" s="2" t="s">
         <v>0</v>
@@ -1487,13 +1517,13 @@
         <v>14</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>56</v>
+        <v>64</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>55</v>
+        <v>63</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>54</v>
+        <v>62</v>
       </c>
       <c r="E18" s="2" t="s">
         <v>3</v>
@@ -1502,27 +1532,29 @@
         <v>1</v>
       </c>
       <c r="G18" s="2">
-        <v>10.0</v>
+        <v>8.0</v>
       </c>
       <c r="H18" s="2">
         <v>10.0</v>
       </c>
       <c r="I18" s="2" t="s">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="J18" s="2">
-        <v>5</v>
-      </c>
-      <c r="K18" s="2"/>
+        <v>4</v>
+      </c>
+      <c r="K18" s="2">
+        <v>1</v>
+      </c>
       <c r="L18" s="2"/>
       <c r="M18" s="2">
         <v>5</v>
       </c>
       <c r="N18" s="2">
-        <v>4.43</v>
+        <v>10.48</v>
       </c>
       <c r="O18" s="2" t="s">
-        <v>53</v>
+        <v>61</v>
       </c>
       <c r="P18" s="2" t="s">
         <v>0</v>
@@ -1533,13 +1565,13 @@
         <v>15</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>52</v>
+        <v>60</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>51</v>
+        <v>59</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>50</v>
+        <v>58</v>
       </c>
       <c r="E19" s="2" t="s">
         <v>3</v>
@@ -1548,27 +1580,29 @@
         <v>1</v>
       </c>
       <c r="G19" s="2">
-        <v>10.0</v>
+        <v>8.0</v>
       </c>
       <c r="H19" s="2">
         <v>10.0</v>
       </c>
       <c r="I19" s="2" t="s">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="J19" s="2">
-        <v>5</v>
-      </c>
-      <c r="K19" s="2"/>
+        <v>4</v>
+      </c>
+      <c r="K19" s="2">
+        <v>1</v>
+      </c>
       <c r="L19" s="2"/>
       <c r="M19" s="2">
         <v>5</v>
       </c>
       <c r="N19" s="2">
-        <v>7.9</v>
+        <v>29.6</v>
       </c>
       <c r="O19" s="2" t="s">
-        <v>49</v>
+        <v>57</v>
       </c>
       <c r="P19" s="2" t="s">
         <v>0</v>
@@ -1579,13 +1613,13 @@
         <v>16</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>48</v>
+        <v>56</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>47</v>
+        <v>55</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>46</v>
+        <v>54</v>
       </c>
       <c r="E20" s="2" t="s">
         <v>3</v>
@@ -1611,10 +1645,10 @@
         <v>5</v>
       </c>
       <c r="N20" s="2">
-        <v>12.17</v>
+        <v>4.43</v>
       </c>
       <c r="O20" s="2" t="s">
-        <v>45</v>
+        <v>53</v>
       </c>
       <c r="P20" s="2" t="s">
         <v>0</v>
@@ -1625,13 +1659,13 @@
         <v>17</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>44</v>
+        <v>52</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>43</v>
+        <v>51</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>42</v>
+        <v>50</v>
       </c>
       <c r="E21" s="2" t="s">
         <v>3</v>
@@ -1657,10 +1691,10 @@
         <v>5</v>
       </c>
       <c r="N21" s="2">
-        <v>2.65</v>
+        <v>7.9</v>
       </c>
       <c r="O21" s="2" t="s">
-        <v>41</v>
+        <v>49</v>
       </c>
       <c r="P21" s="2" t="s">
         <v>0</v>
@@ -1671,13 +1705,13 @@
         <v>18</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>40</v>
+        <v>48</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>39</v>
+        <v>47</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>38</v>
+        <v>46</v>
       </c>
       <c r="E22" s="2" t="s">
         <v>3</v>
@@ -1686,29 +1720,27 @@
         <v>1</v>
       </c>
       <c r="G22" s="2">
-        <v>8.0</v>
+        <v>10.0</v>
       </c>
       <c r="H22" s="2">
         <v>10.0</v>
       </c>
       <c r="I22" s="2" t="s">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="J22" s="2">
-        <v>4</v>
-      </c>
-      <c r="K22" s="2">
-        <v>1</v>
-      </c>
+        <v>5</v>
+      </c>
+      <c r="K22" s="2"/>
       <c r="L22" s="2"/>
       <c r="M22" s="2">
         <v>5</v>
       </c>
       <c r="N22" s="2">
-        <v>14.27</v>
+        <v>12.17</v>
       </c>
       <c r="O22" s="2" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="P22" s="2" t="s">
         <v>0</v>
@@ -1719,44 +1751,42 @@
         <v>19</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>36</v>
+        <v>44</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>35</v>
+        <v>43</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>34</v>
+        <v>42</v>
       </c>
       <c r="E23" s="2" t="s">
         <v>3</v>
       </c>
       <c r="F23" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G23" s="2">
-        <v>6.0</v>
+        <v>10.0</v>
       </c>
       <c r="H23" s="2">
         <v>10.0</v>
       </c>
       <c r="I23" s="2" t="s">
-        <v>29</v>
+        <v>2</v>
       </c>
       <c r="J23" s="2">
-        <v>3</v>
-      </c>
-      <c r="K23" s="2">
-        <v>2</v>
-      </c>
+        <v>5</v>
+      </c>
+      <c r="K23" s="2"/>
       <c r="L23" s="2"/>
       <c r="M23" s="2">
         <v>5</v>
       </c>
       <c r="N23" s="2">
-        <v>1.62</v>
+        <v>2.65</v>
       </c>
       <c r="O23" s="2" t="s">
-        <v>33</v>
+        <v>41</v>
       </c>
       <c r="P23" s="2" t="s">
         <v>0</v>
@@ -1767,13 +1797,13 @@
         <v>20</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>32</v>
+        <v>40</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>31</v>
+        <v>39</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>30</v>
+        <v>38</v>
       </c>
       <c r="E24" s="2" t="s">
         <v>3</v>
@@ -1782,29 +1812,29 @@
         <v>1</v>
       </c>
       <c r="G24" s="2">
-        <v>6.0</v>
+        <v>8.0</v>
       </c>
       <c r="H24" s="2">
         <v>10.0</v>
       </c>
       <c r="I24" s="2" t="s">
-        <v>29</v>
+        <v>12</v>
       </c>
       <c r="J24" s="2">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K24" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L24" s="2"/>
       <c r="M24" s="2">
         <v>5</v>
       </c>
       <c r="N24" s="2">
-        <v>14.25</v>
+        <v>14.27</v>
       </c>
       <c r="O24" s="2" t="s">
-        <v>28</v>
+        <v>37</v>
       </c>
       <c r="P24" s="2" t="s">
         <v>0</v>
@@ -1815,13 +1845,13 @@
         <v>21</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>27</v>
+        <v>36</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>26</v>
+        <v>35</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>25</v>
+        <v>34</v>
       </c>
       <c r="E25" s="2" t="s">
         <v>3</v>
@@ -1830,27 +1860,29 @@
         <v>2</v>
       </c>
       <c r="G25" s="2">
-        <v>10.0</v>
+        <v>6.0</v>
       </c>
       <c r="H25" s="2">
         <v>10.0</v>
       </c>
       <c r="I25" s="2" t="s">
-        <v>2</v>
+        <v>29</v>
       </c>
       <c r="J25" s="2">
-        <v>5</v>
-      </c>
-      <c r="K25" s="2"/>
+        <v>3</v>
+      </c>
+      <c r="K25" s="2">
+        <v>2</v>
+      </c>
       <c r="L25" s="2"/>
       <c r="M25" s="2">
         <v>5</v>
       </c>
       <c r="N25" s="2">
-        <v>3.77</v>
+        <v>1.62</v>
       </c>
       <c r="O25" s="2" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
       <c r="P25" s="2" t="s">
         <v>0</v>
@@ -1861,13 +1893,13 @@
         <v>22</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>23</v>
+        <v>32</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>22</v>
+        <v>31</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>21</v>
+        <v>30</v>
       </c>
       <c r="E26" s="2" t="s">
         <v>3</v>
@@ -1876,27 +1908,29 @@
         <v>1</v>
       </c>
       <c r="G26" s="2">
-        <v>10.0</v>
+        <v>6.0</v>
       </c>
       <c r="H26" s="2">
         <v>10.0</v>
       </c>
       <c r="I26" s="2" t="s">
-        <v>2</v>
+        <v>29</v>
       </c>
       <c r="J26" s="2">
-        <v>5</v>
-      </c>
-      <c r="K26" s="2"/>
+        <v>3</v>
+      </c>
+      <c r="K26" s="2">
+        <v>2</v>
+      </c>
       <c r="L26" s="2"/>
       <c r="M26" s="2">
         <v>5</v>
       </c>
       <c r="N26" s="2">
-        <v>5.62</v>
+        <v>14.25</v>
       </c>
       <c r="O26" s="2" t="s">
-        <v>20</v>
+        <v>28</v>
       </c>
       <c r="P26" s="2" t="s">
         <v>0</v>
@@ -1907,44 +1941,42 @@
         <v>23</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>19</v>
+        <v>27</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>18</v>
+        <v>26</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="E27" s="2" t="s">
         <v>3</v>
       </c>
       <c r="F27" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G27" s="2">
-        <v>8.0</v>
+        <v>10.0</v>
       </c>
       <c r="H27" s="2">
         <v>10.0</v>
       </c>
       <c r="I27" s="2" t="s">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="J27" s="2">
-        <v>4</v>
-      </c>
-      <c r="K27" s="2">
-        <v>1</v>
-      </c>
+        <v>5</v>
+      </c>
+      <c r="K27" s="2"/>
       <c r="L27" s="2"/>
       <c r="M27" s="2">
         <v>5</v>
       </c>
       <c r="N27" s="2">
-        <v>29.93</v>
+        <v>3.77</v>
       </c>
       <c r="O27" s="2" t="s">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="P27" s="2" t="s">
         <v>0</v>
@@ -1955,44 +1987,42 @@
         <v>24</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="E28" s="2" t="s">
         <v>3</v>
       </c>
       <c r="F28" s="2">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G28" s="2">
-        <v>8.0</v>
+        <v>10.0</v>
       </c>
       <c r="H28" s="2">
         <v>10.0</v>
       </c>
       <c r="I28" s="2" t="s">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="J28" s="2">
-        <v>4</v>
-      </c>
-      <c r="K28" s="2">
-        <v>1</v>
-      </c>
+        <v>5</v>
+      </c>
+      <c r="K28" s="2"/>
       <c r="L28" s="2"/>
       <c r="M28" s="2">
         <v>5</v>
       </c>
       <c r="N28" s="2">
-        <v>69.77</v>
+        <v>5.62</v>
       </c>
       <c r="O28" s="2" t="s">
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="P28" s="2" t="s">
         <v>0</v>
@@ -2003,13 +2033,13 @@
         <v>25</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>9</v>
+        <v>18</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="E29" s="2" t="s">
         <v>3</v>
@@ -2018,27 +2048,29 @@
         <v>1</v>
       </c>
       <c r="G29" s="2">
-        <v>10.0</v>
+        <v>8.0</v>
       </c>
       <c r="H29" s="2">
         <v>10.0</v>
       </c>
       <c r="I29" s="2" t="s">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="J29" s="2">
-        <v>5</v>
-      </c>
-      <c r="K29" s="2"/>
+        <v>4</v>
+      </c>
+      <c r="K29" s="2">
+        <v>1</v>
+      </c>
       <c r="L29" s="2"/>
       <c r="M29" s="2">
         <v>5</v>
       </c>
       <c r="N29" s="2">
-        <v>20.27</v>
+        <v>29.93</v>
       </c>
       <c r="O29" s="2" t="s">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="P29" s="2" t="s">
         <v>0</v>
@@ -2049,44 +2081,138 @@
         <v>26</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="D30" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="E30" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="F30" s="2">
+        <v>3</v>
+      </c>
+      <c r="G30" s="2">
+        <v>8.0</v>
+      </c>
+      <c r="H30" s="2">
+        <v>10.0</v>
+      </c>
+      <c r="I30" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="J30" s="2">
         <v>4</v>
       </c>
-      <c r="E30" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="F30" s="2">
-        <v>1</v>
-      </c>
-      <c r="G30" s="2">
-        <v>10.0</v>
-      </c>
-      <c r="H30" s="2">
-        <v>10.0</v>
-      </c>
-      <c r="I30" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="J30" s="2">
-        <v>5</v>
-      </c>
-      <c r="K30" s="2"/>
+      <c r="K30" s="2">
+        <v>1</v>
+      </c>
       <c r="L30" s="2"/>
       <c r="M30" s="2">
         <v>5</v>
       </c>
       <c r="N30" s="2">
+        <v>69.77</v>
+      </c>
+      <c r="O30" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="P30" s="2" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="1:16">
+      <c r="A31" s="2">
+        <v>27</v>
+      </c>
+      <c r="B31" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="C31" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D31" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E31" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="F31" s="2">
+        <v>1</v>
+      </c>
+      <c r="G31" s="2">
+        <v>10.0</v>
+      </c>
+      <c r="H31" s="2">
+        <v>10.0</v>
+      </c>
+      <c r="I31" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="J31" s="2">
+        <v>5</v>
+      </c>
+      <c r="K31" s="2"/>
+      <c r="L31" s="2"/>
+      <c r="M31" s="2">
+        <v>5</v>
+      </c>
+      <c r="N31" s="2">
+        <v>20.27</v>
+      </c>
+      <c r="O31" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="P31" s="2" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="1:16">
+      <c r="A32" s="2">
+        <v>28</v>
+      </c>
+      <c r="B32" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="C32" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="D32" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="E32" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="F32" s="2">
+        <v>1</v>
+      </c>
+      <c r="G32" s="2">
+        <v>10.0</v>
+      </c>
+      <c r="H32" s="2">
+        <v>10.0</v>
+      </c>
+      <c r="I32" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="J32" s="2">
+        <v>5</v>
+      </c>
+      <c r="K32" s="2"/>
+      <c r="L32" s="2"/>
+      <c r="M32" s="2">
+        <v>5</v>
+      </c>
+      <c r="N32" s="2">
         <v>21.33</v>
       </c>
-      <c r="O30" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="P30" s="2" t="s">
+      <c r="O32" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="P32" s="2" t="s">
         <v>0</v>
       </c>
     </row>

--- a/2lit_online.xlsx
+++ b/2lit_online.xlsx
@@ -428,7 +428,7 @@
     <t>الدرجة الكاملة: 10 | درجة النجاح: 5.00</t>
   </si>
   <si>
-    <t>تاريخ التصدير: 2026-04-05 16:57</t>
+    <t>تاريخ التصدير: 2026-04-05 17:09</t>
   </si>
 </sst>
 </file>

--- a/2lit_online.xlsx
+++ b/2lit_online.xlsx
@@ -428,7 +428,7 @@
     <t>الدرجة الكاملة: 10 | درجة النجاح: 5.00</t>
   </si>
   <si>
-    <t>تاريخ التصدير: 2026-04-05 17:09</t>
+    <t>تاريخ التصدير: 2026-04-05 17:45</t>
   </si>
 </sst>
 </file>

--- a/2lit_online.xlsx
+++ b/2lit_online.xlsx
@@ -428,7 +428,7 @@
     <t>الدرجة الكاملة: 10 | درجة النجاح: 5.00</t>
   </si>
   <si>
-    <t>تاريخ التصدير: 2026-04-05 17:45</t>
+    <t>تاريخ التصدير: 2026-04-06 16:51</t>
   </si>
 </sst>
 </file>
